--- a/TUCUMAN 1061/Diciembre/tucuman Diciembre.xlsx
+++ b/TUCUMAN 1061/Diciembre/tucuman Diciembre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\TUCUMAN 1061\Diciembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\TUCUMAN 1061\Diciembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57C41C90-A046-452F-A0E9-C6ADF956CB8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB7DFC91-B935-44CD-9CFE-5B7762455206}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Gastos" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Calculo Servicios  (2)'!$A$6:$H$23</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Gastos!$A$2:$H$57</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Gastos!$A$2:$H$58</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">Planilla!$A$1:$S$39</definedName>
     <definedName name="CantOper" localSheetId="2">#REF!</definedName>
     <definedName name="CantOper">#REF!</definedName>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="166">
   <si>
     <t>Domicilio:</t>
   </si>
@@ -506,9 +506,6 @@
     <t xml:space="preserve">Banco santander - C DE P TUCUMAN 1061 1063 - Nro. De cuenta : 39-022068/6
 CBU: 0720039720000002206868
 </t>
-  </si>
-  <si>
-    <t>Articulios de limpieza</t>
   </si>
   <si>
     <t>5 - GASTOS BANCARIOS</t>
@@ -527,18 +524,9 @@
 ¡Muchas gracias por la colaboración! 🙌</t>
   </si>
   <si>
-    <t xml:space="preserve">Sr. Leonardo Balcazza trabajo en medianera (Altura) - Diferencia </t>
-  </si>
-  <si>
     <t>Seguro OBLIGATORIO DE CONSORCIO - POLIZA Nro. 191195427 - Mercantil Andina</t>
   </si>
   <si>
-    <t xml:space="preserve">Gustavo padron - Contador - Honorarios </t>
-  </si>
-  <si>
-    <t>Prevision ordinaria - Edesur</t>
-  </si>
-  <si>
     <t>subidos en n0v 2025</t>
   </si>
   <si>
@@ -554,9 +542,6 @@
     <t>SOLICITAMOS POR FAVOR QUE, SI REALIZAN EL PAGO ANTES DE LA FECHA DEL PRIMER VENCIMIENTO (EN ESTE CASO, EL 15/12), ABONEN ÚNICAMENTE EL MONTO CORRESPONDIENTE A DICHO VENCIMIENTO Y NO EL DEL SEGUNDO.</t>
   </si>
   <si>
-    <t>la habiamos puesto impaga</t>
-  </si>
-  <si>
     <t>VTO: 15/01</t>
   </si>
   <si>
@@ -573,6 +558,18 @@
   </si>
   <si>
     <t>Servisur -  Fotocelula con cableado</t>
+  </si>
+  <si>
+    <t>SAC</t>
+  </si>
+  <si>
+    <t>Alterini Guido - Jardinero</t>
+  </si>
+  <si>
+    <t>Celeste</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prevision ordinaria </t>
   </si>
 </sst>
 </file>
@@ -847,7 +844,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -1391,7 +1387,7 @@
     <xf numFmtId="167" fontId="24" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="1" fontId="24" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="295">
+  <cellXfs count="290">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1519,9 +1515,6 @@
     <xf numFmtId="164" fontId="17" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -1659,9 +1652,6 @@
     <xf numFmtId="0" fontId="21" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="30" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -1674,26 +1664,8 @@
     <xf numFmtId="164" fontId="17" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="18" fillId="9" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="18" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="28" fillId="9" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="18" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="17" fillId="9" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="6" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="0" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="37" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="6" fontId="2" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="44" fontId="0" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="2" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="2" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1714,18 +1686,6 @@
     <xf numFmtId="6" fontId="2" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="30" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="21" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="18" fillId="7" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="17" fillId="7" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="17" fillId="7" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="17" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="18" fillId="7" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="18" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1870,33 +1830,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="43" fontId="36" fillId="9" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="36" fillId="9" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="36" fillId="9" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="36" fillId="9" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="36" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="36" fillId="9" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="36" fillId="9" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="36" fillId="9" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="36" fillId="9" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="43" fontId="13" fillId="11" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1951,8 +1884,68 @@
     <xf numFmtId="1" fontId="25" fillId="8" borderId="29" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="34" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="34" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="36" fillId="9" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="36" fillId="9" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="36" fillId="9" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="36" fillId="9" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="36" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="36" fillId="9" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="36" fillId="9" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="36" fillId="9" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="36" fillId="9" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="17" fillId="5" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="28" fillId="5" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="2" fontId="17" fillId="5" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="7" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="37" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="6" fontId="8" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="8" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -2296,15 +2289,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:N56"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:N57"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2317,18 +2310,18 @@
       <c r="G2" s="1"/>
       <c r="H2" s="4"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
       <c r="D3" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="218">
+      <c r="E3" s="194">
         <v>1153202676</v>
       </c>
-      <c r="F3" s="218"/>
+      <c r="F3" s="194"/>
       <c r="H3" s="6"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
       <c r="D4" s="12" t="s">
         <v>2</v>
@@ -2338,41 +2331,41 @@
       </c>
       <c r="H4" s="6"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
       <c r="D5" t="s">
         <v>17</v>
       </c>
       <c r="H5" s="6"/>
-      <c r="J5" s="159"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J5" s="158"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
-      <c r="D6" s="219" t="s">
+      <c r="D6" s="195" t="s">
         <v>145</v>
       </c>
-      <c r="E6" s="219"/>
-      <c r="F6" s="219"/>
-      <c r="G6" s="219"/>
-      <c r="H6" s="220"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E6" s="195"/>
+      <c r="F6" s="195"/>
+      <c r="G6" s="195"/>
+      <c r="H6" s="196"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
-      <c r="D7" s="219"/>
-      <c r="E7" s="219"/>
-      <c r="F7" s="219"/>
-      <c r="G7" s="219"/>
-      <c r="H7" s="220"/>
-    </row>
-    <row r="8" spans="1:10" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D7" s="195"/>
+      <c r="E7" s="195"/>
+      <c r="F7" s="195"/>
+      <c r="G7" s="195"/>
+      <c r="H7" s="196"/>
+    </row>
+    <row r="8" spans="1:10" ht="22.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
-      <c r="D8" s="219"/>
-      <c r="E8" s="219"/>
-      <c r="F8" s="219"/>
-      <c r="G8" s="219"/>
-      <c r="H8" s="220"/>
-    </row>
-    <row r="9" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+      <c r="D8" s="195"/>
+      <c r="E8" s="195"/>
+      <c r="F8" s="195"/>
+      <c r="G8" s="195"/>
+      <c r="H8" s="196"/>
+    </row>
+    <row r="9" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
         <v>3</v>
       </c>
@@ -2380,15 +2373,15 @@
       <c r="C9" s="10"/>
       <c r="D9" s="10"/>
       <c r="E9" s="10" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="F9" s="10"/>
       <c r="G9" s="11"/>
-      <c r="H9" s="162" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H9" s="161" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -2398,11 +2391,11 @@
       <c r="G10" s="1"/>
       <c r="H10" s="4"/>
     </row>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
       <c r="H11" s="6"/>
     </row>
-    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>4</v>
       </c>
@@ -2411,7 +2404,7 @@
       </c>
       <c r="H12" s="6"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="7"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -2421,477 +2414,532 @@
       <c r="G13" s="2"/>
       <c r="H13" s="8"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="232" t="s">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="208" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="232"/>
-      <c r="C14" s="232"/>
-      <c r="D14" s="232"/>
-      <c r="E14" s="232"/>
-      <c r="F14" s="232"/>
-      <c r="G14" s="232"/>
-      <c r="H14" s="232"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="5"/>
-      <c r="H15" s="186"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
+      <c r="B14" s="208"/>
+      <c r="C14" s="208"/>
+      <c r="D14" s="208"/>
+      <c r="E14" s="208"/>
+      <c r="F14" s="208"/>
+      <c r="G14" s="208"/>
+      <c r="H14" s="208"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="273"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="274"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="273" t="s">
         <v>48</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="H16" s="187">
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="275">
         <f>392270+392270*2%</f>
         <v>400115.4</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" s="188" t="s">
-        <v>163</v>
-      </c>
-      <c r="H17" s="294">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="273" t="s">
+        <v>162</v>
+      </c>
+      <c r="B17" s="17"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="275">
+        <f>H16/2</f>
+        <v>200057.7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="276" t="s">
+        <v>158</v>
+      </c>
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="275">
         <v>4030.28</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="189" t="s">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="277" t="s">
         <v>5</v>
       </c>
-      <c r="B18" s="190"/>
-      <c r="C18" s="190"/>
-      <c r="D18" s="190"/>
-      <c r="E18" s="190"/>
-      <c r="F18" s="190"/>
-      <c r="G18" s="190"/>
-      <c r="H18" s="191">
-        <f>SUM(H15:H17)</f>
-        <v>404145.68000000005</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="7"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="8"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="233" t="s">
+      <c r="B19" s="278"/>
+      <c r="C19" s="278"/>
+      <c r="D19" s="278"/>
+      <c r="E19" s="278"/>
+      <c r="F19" s="278"/>
+      <c r="G19" s="278"/>
+      <c r="H19" s="279">
+        <f>SUM(H15:H18)</f>
+        <v>604203.38000000012</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="280"/>
+      <c r="B20" s="281"/>
+      <c r="C20" s="281"/>
+      <c r="D20" s="281"/>
+      <c r="E20" s="281"/>
+      <c r="F20" s="281"/>
+      <c r="G20" s="281"/>
+      <c r="H20" s="282"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="283" t="s">
         <v>6</v>
       </c>
-      <c r="B20" s="234"/>
-      <c r="C20" s="234"/>
-      <c r="D20" s="234"/>
-      <c r="E20" s="234"/>
-      <c r="F20" s="234"/>
-      <c r="G20" s="234"/>
-      <c r="H20" s="235"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" s="5" t="s">
+      <c r="B21" s="284"/>
+      <c r="C21" s="284"/>
+      <c r="D21" s="284"/>
+      <c r="E21" s="284"/>
+      <c r="F21" s="284"/>
+      <c r="G21" s="284"/>
+      <c r="H21" s="285"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="273" t="s">
         <v>47</v>
       </c>
-      <c r="C21" s="192"/>
-      <c r="H21" s="293">
+      <c r="B22" s="17"/>
+      <c r="C22" s="286"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="18">
         <v>17684.560000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A22" s="5" t="s">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="273" t="s">
         <v>46</v>
       </c>
-      <c r="C22" s="192"/>
-      <c r="H22" s="293">
+      <c r="B23" s="17"/>
+      <c r="C23" s="286"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="18">
         <v>1051844.78</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A23" s="189" t="s">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="277" t="s">
         <v>7</v>
       </c>
-      <c r="B23" s="190"/>
-      <c r="C23" s="190"/>
-      <c r="D23" s="190"/>
-      <c r="E23" s="190"/>
-      <c r="F23" s="190"/>
-      <c r="G23" s="190"/>
-      <c r="H23" s="194">
-        <f>SUM(H21:H22)</f>
+      <c r="B24" s="278"/>
+      <c r="C24" s="278"/>
+      <c r="D24" s="278"/>
+      <c r="E24" s="278"/>
+      <c r="F24" s="278"/>
+      <c r="G24" s="278"/>
+      <c r="H24" s="287">
+        <f>SUM(H22:H23)</f>
         <v>1069529.3400000001</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A24" s="232" t="s">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="288" t="s">
         <v>49</v>
       </c>
-      <c r="B24" s="232"/>
-      <c r="C24" s="232"/>
-      <c r="D24" s="232"/>
-      <c r="E24" s="232"/>
-      <c r="F24" s="232"/>
-      <c r="G24" s="232"/>
-      <c r="H24" s="232"/>
-      <c r="J24" s="18"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A25" s="188" t="s">
-        <v>152</v>
-      </c>
-      <c r="C25" s="192"/>
-      <c r="H25" s="293">
-        <v>48079.519999999997</v>
-      </c>
-      <c r="I25" s="13"/>
-      <c r="J25" s="13"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A26" s="188" t="s">
-        <v>146</v>
-      </c>
-      <c r="C26" s="192"/>
-      <c r="H26" s="193">
-        <v>0</v>
+      <c r="B25" s="288"/>
+      <c r="C25" s="288"/>
+      <c r="D25" s="288"/>
+      <c r="E25" s="288"/>
+      <c r="F25" s="288"/>
+      <c r="G25" s="288"/>
+      <c r="H25" s="288"/>
+      <c r="J25" s="18"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="276" t="s">
+        <v>150</v>
+      </c>
+      <c r="B26" s="17"/>
+      <c r="C26" s="286"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="18">
+        <v>48099.519999999997</v>
       </c>
       <c r="I26" s="13"/>
       <c r="J26" s="13"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A27" s="188" t="s">
-        <v>165</v>
-      </c>
-      <c r="C27" s="192"/>
-      <c r="H27" s="293">
-        <v>200000</v>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="276" t="s">
+        <v>163</v>
+      </c>
+      <c r="B27" s="17"/>
+      <c r="C27" s="286"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="18">
+        <v>150000</v>
       </c>
       <c r="I27" s="13"/>
       <c r="J27" s="13"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A28" s="188" t="s">
-        <v>166</v>
-      </c>
-      <c r="C28" s="192"/>
-      <c r="H28" s="293">
-        <v>30000</v>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="276" t="s">
+        <v>160</v>
+      </c>
+      <c r="B28" s="17"/>
+      <c r="C28" s="286"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="18">
+        <v>20000</v>
       </c>
       <c r="I28" s="13"/>
       <c r="J28" s="13"/>
     </row>
-    <row r="29" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="188" t="s">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="276" t="s">
+        <v>161</v>
+      </c>
+      <c r="B29" s="17"/>
+      <c r="C29" s="286"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="17"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="18">
+        <v>30000</v>
+      </c>
+      <c r="I29" s="13"/>
+      <c r="J29" s="13"/>
+    </row>
+    <row r="30" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="276" t="s">
         <v>130</v>
       </c>
-      <c r="H29" s="293">
+      <c r="B30" s="17"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="17"/>
+      <c r="G30" s="17"/>
+      <c r="H30" s="18">
         <v>80000</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A30" s="189" t="s">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="277" t="s">
         <v>8</v>
       </c>
-      <c r="B30" s="190"/>
-      <c r="C30" s="190"/>
-      <c r="D30" s="190"/>
-      <c r="E30" s="190"/>
-      <c r="F30" s="190"/>
-      <c r="G30" s="190"/>
-      <c r="H30" s="194">
-        <f>SUM(H25:H29)</f>
-        <v>358079.52</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A31" s="233" t="s">
+      <c r="B31" s="278"/>
+      <c r="C31" s="278"/>
+      <c r="D31" s="278"/>
+      <c r="E31" s="278"/>
+      <c r="F31" s="278"/>
+      <c r="G31" s="278"/>
+      <c r="H31" s="287">
+        <f>SUM(H26:H30)</f>
+        <v>328099.52</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="283" t="s">
         <v>50</v>
       </c>
-      <c r="B31" s="234"/>
-      <c r="C31" s="234"/>
-      <c r="D31" s="234"/>
-      <c r="E31" s="234"/>
-      <c r="F31" s="234"/>
-      <c r="G31" s="234"/>
-      <c r="H31" s="235"/>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A32" s="5" t="s">
+      <c r="B32" s="284"/>
+      <c r="C32" s="284"/>
+      <c r="D32" s="284"/>
+      <c r="E32" s="284"/>
+      <c r="F32" s="284"/>
+      <c r="G32" s="284"/>
+      <c r="H32" s="285"/>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A33" s="273" t="s">
         <v>9</v>
       </c>
-      <c r="C32" t="s">
+      <c r="B33" s="17"/>
+      <c r="C33" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="H32" s="195">
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="289">
         <v>97600</v>
       </c>
-      <c r="I32" s="31"/>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="H33" s="195">
-        <v>0</v>
-      </c>
       <c r="I33" s="31"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="189" t="s">
-        <v>164</v>
-      </c>
-      <c r="B34" s="190"/>
-      <c r="C34" s="190"/>
-      <c r="D34" s="190"/>
-      <c r="E34" s="190"/>
-      <c r="F34" s="190"/>
-      <c r="G34" s="190"/>
-      <c r="H34" s="196">
-        <f>SUM(H32:H33)</f>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34" s="273"/>
+      <c r="B34" s="17"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="17"/>
+      <c r="H34" s="289">
+        <v>0</v>
+      </c>
+      <c r="I34" s="31"/>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35" s="180" t="s">
+        <v>159</v>
+      </c>
+      <c r="B35" s="181"/>
+      <c r="C35" s="181"/>
+      <c r="D35" s="181"/>
+      <c r="E35" s="181"/>
+      <c r="F35" s="181"/>
+      <c r="G35" s="181"/>
+      <c r="H35" s="182">
+        <f>SUM(H33:H34)</f>
         <v>97600</v>
       </c>
-      <c r="I34" s="31"/>
-      <c r="N34" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="5"/>
-      <c r="H35" s="197"/>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="233" t="s">
+      <c r="I35" s="31"/>
+      <c r="N35" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A36" s="5"/>
+      <c r="H36" s="183"/>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A37" s="209" t="s">
+        <v>146</v>
+      </c>
+      <c r="B37" s="210"/>
+      <c r="C37" s="210"/>
+      <c r="D37" s="210"/>
+      <c r="E37" s="210"/>
+      <c r="F37" s="210"/>
+      <c r="G37" s="210"/>
+      <c r="H37" s="211"/>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A38" s="184" t="s">
         <v>147</v>
       </c>
-      <c r="B36" s="234"/>
-      <c r="C36" s="234"/>
-      <c r="D36" s="234"/>
-      <c r="E36" s="234"/>
-      <c r="F36" s="234"/>
-      <c r="G36" s="234"/>
-      <c r="H36" s="235"/>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="198" t="s">
-        <v>148</v>
-      </c>
-      <c r="B37" s="199"/>
-      <c r="C37" s="199"/>
-      <c r="D37" s="199"/>
-      <c r="E37" s="199"/>
-      <c r="F37" s="199"/>
-      <c r="G37" s="199"/>
-      <c r="H37" s="200">
-        <v>19863.259999999998</v>
-      </c>
-      <c r="J37" s="14"/>
-    </row>
-    <row r="38" spans="1:14" s="15" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="201" t="s">
+      <c r="B38" s="185"/>
+      <c r="C38" s="185"/>
+      <c r="D38" s="185"/>
+      <c r="E38" s="185"/>
+      <c r="F38" s="185"/>
+      <c r="G38" s="185"/>
+      <c r="H38" s="186">
+        <v>17108.68</v>
+      </c>
+      <c r="J38" s="14"/>
+    </row>
+    <row r="39" spans="1:14" s="15" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A39" s="187" t="s">
         <v>15</v>
       </c>
-      <c r="B38" s="202"/>
-      <c r="C38" s="202"/>
-      <c r="D38" s="202"/>
-      <c r="E38" s="202"/>
-      <c r="F38" s="202"/>
-      <c r="G38" s="202"/>
-      <c r="H38" s="203">
-        <f>H18+H23+H30+H34+H37</f>
-        <v>1949217.8</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
-      <c r="A39" s="204" t="s">
-        <v>154</v>
-      </c>
-      <c r="B39" s="205"/>
-      <c r="C39" s="205"/>
-      <c r="D39" s="205"/>
-      <c r="E39" s="205"/>
-      <c r="F39" s="205"/>
-      <c r="G39" s="205"/>
-      <c r="H39" s="206">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="223" t="s">
+      <c r="B39" s="188"/>
+      <c r="C39" s="188"/>
+      <c r="D39" s="188"/>
+      <c r="E39" s="188"/>
+      <c r="F39" s="188"/>
+      <c r="G39" s="188"/>
+      <c r="H39" s="189">
+        <f>H19+H24+H31+H35+H38</f>
+        <v>2116540.9200000004</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" s="13" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A40" s="190" t="s">
+        <v>165</v>
+      </c>
+      <c r="B40" s="191"/>
+      <c r="C40" s="191"/>
+      <c r="D40" s="191"/>
+      <c r="E40" s="191"/>
+      <c r="F40" s="191"/>
+      <c r="G40" s="191"/>
+      <c r="H40" s="192"/>
+    </row>
+    <row r="41" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="199" t="s">
         <v>12</v>
       </c>
-      <c r="B40" s="224"/>
-      <c r="C40" s="224"/>
-      <c r="D40" s="224"/>
-      <c r="E40" s="224"/>
-      <c r="F40" s="224"/>
-      <c r="G40" s="224"/>
-      <c r="H40" s="225"/>
-      <c r="I40" s="141"/>
-      <c r="K40" s="141"/>
-    </row>
-    <row r="41" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="226"/>
-      <c r="B41" s="227"/>
-      <c r="C41" s="227"/>
-      <c r="D41" s="227"/>
-      <c r="E41" s="227"/>
-      <c r="F41" s="227"/>
-      <c r="G41" s="227"/>
-      <c r="H41" s="228"/>
-    </row>
-    <row r="42" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="242" t="s">
-        <v>151</v>
-      </c>
-      <c r="B42" s="243"/>
-      <c r="C42" s="243"/>
-      <c r="D42" s="243"/>
-      <c r="E42" s="243"/>
-      <c r="F42" s="243"/>
-      <c r="G42" s="244"/>
-      <c r="H42" s="207">
-        <f>520000-350000</f>
-        <v>170000</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="236"/>
-      <c r="B43" s="237"/>
-      <c r="C43" s="237"/>
-      <c r="D43" s="237"/>
-      <c r="E43" s="237"/>
-      <c r="F43" s="237"/>
-      <c r="G43" s="238"/>
-      <c r="H43" s="22"/>
-    </row>
-    <row r="44" spans="1:14" s="13" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="239" t="s">
+      <c r="B41" s="200"/>
+      <c r="C41" s="200"/>
+      <c r="D41" s="200"/>
+      <c r="E41" s="200"/>
+      <c r="F41" s="200"/>
+      <c r="G41" s="200"/>
+      <c r="H41" s="201"/>
+      <c r="I41" s="140"/>
+      <c r="K41" s="140"/>
+    </row>
+    <row r="42" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="202"/>
+      <c r="B42" s="203"/>
+      <c r="C42" s="203"/>
+      <c r="D42" s="203"/>
+      <c r="E42" s="203"/>
+      <c r="F42" s="203"/>
+      <c r="G42" s="203"/>
+      <c r="H42" s="204"/>
+    </row>
+    <row r="43" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="218"/>
+      <c r="B43" s="219"/>
+      <c r="C43" s="219"/>
+      <c r="D43" s="219"/>
+      <c r="E43" s="219"/>
+      <c r="F43" s="219"/>
+      <c r="G43" s="220"/>
+      <c r="H43" s="193"/>
+    </row>
+    <row r="44" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="212"/>
+      <c r="B44" s="213"/>
+      <c r="C44" s="213"/>
+      <c r="D44" s="213"/>
+      <c r="E44" s="213"/>
+      <c r="F44" s="213"/>
+      <c r="G44" s="214"/>
+      <c r="H44" s="22"/>
+    </row>
+    <row r="45" spans="1:14" s="13" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="215" t="s">
         <v>16</v>
       </c>
-      <c r="B44" s="240"/>
-      <c r="C44" s="240"/>
-      <c r="D44" s="240"/>
-      <c r="E44" s="240"/>
-      <c r="F44" s="240"/>
-      <c r="G44" s="241"/>
-      <c r="H44" s="23">
-        <f>SUM(H42:H43)</f>
-        <v>170000</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14" s="13" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="157"/>
-      <c r="B45" s="157"/>
-      <c r="C45" s="157"/>
-      <c r="D45" s="157"/>
-      <c r="E45" s="157"/>
-      <c r="F45" s="157"/>
-      <c r="G45" s="157"/>
-      <c r="H45" s="158"/>
-    </row>
-    <row r="46" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H46" s="17"/>
-      <c r="J46" s="14"/>
-    </row>
-    <row r="47" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="221" t="s">
+      <c r="B45" s="216"/>
+      <c r="C45" s="216"/>
+      <c r="D45" s="216"/>
+      <c r="E45" s="216"/>
+      <c r="F45" s="216"/>
+      <c r="G45" s="217"/>
+      <c r="H45" s="23">
+        <f>SUM(H43:H44)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" s="13" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="156"/>
+      <c r="B46" s="156"/>
+      <c r="C46" s="156"/>
+      <c r="D46" s="156"/>
+      <c r="E46" s="156"/>
+      <c r="F46" s="156"/>
+      <c r="G46" s="156"/>
+      <c r="H46" s="157"/>
+    </row>
+    <row r="47" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H47" s="17"/>
+      <c r="J47" s="14"/>
+    </row>
+    <row r="48" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="197" t="s">
         <v>131</v>
       </c>
-      <c r="B47" s="221"/>
-      <c r="C47" s="221"/>
-      <c r="D47" s="221"/>
-      <c r="E47" s="221"/>
-      <c r="F47" s="221"/>
-      <c r="G47" s="221"/>
-      <c r="H47" s="21">
-        <f>+H38+H39</f>
-        <v>2449217.7999999998</v>
-      </c>
-      <c r="J47" s="141"/>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="17"/>
-      <c r="B48" s="17"/>
-      <c r="C48" s="17"/>
-      <c r="D48" s="17"/>
-      <c r="E48" s="17"/>
-      <c r="F48" s="17"/>
-      <c r="G48" s="17"/>
-      <c r="H48" s="17"/>
-    </row>
-    <row r="49" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="19" t="s">
+      <c r="B48" s="197"/>
+      <c r="C48" s="197"/>
+      <c r="D48" s="197"/>
+      <c r="E48" s="197"/>
+      <c r="F48" s="197"/>
+      <c r="G48" s="197"/>
+      <c r="H48" s="21">
+        <f>+H39+H40</f>
+        <v>2116540.9200000004</v>
+      </c>
+      <c r="J48" s="140"/>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49" s="17"/>
+      <c r="B49" s="17"/>
+      <c r="C49" s="17"/>
+      <c r="D49" s="17"/>
+      <c r="E49" s="17"/>
+      <c r="F49" s="17"/>
+      <c r="G49" s="17"/>
+      <c r="H49" s="17"/>
+    </row>
+    <row r="50" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A50" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="B49" s="20"/>
-      <c r="C49" s="20"/>
-      <c r="D49" s="20"/>
-      <c r="E49" s="20"/>
-      <c r="F49" s="20"/>
-      <c r="G49" s="20"/>
-      <c r="H49" s="24">
-        <f>H44</f>
-        <v>170000</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A50" s="17"/>
-      <c r="B50" s="17"/>
-      <c r="C50" s="17"/>
-      <c r="D50" s="17"/>
-      <c r="E50" s="17"/>
-      <c r="F50" s="17"/>
-      <c r="G50" s="17"/>
-      <c r="H50" s="17"/>
-    </row>
-    <row r="51" spans="1:10" ht="18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="229" t="s">
+      <c r="B50" s="20"/>
+      <c r="C50" s="20"/>
+      <c r="D50" s="20"/>
+      <c r="E50" s="20"/>
+      <c r="F50" s="20"/>
+      <c r="G50" s="20"/>
+      <c r="H50" s="24">
+        <f>H45</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A51" s="17"/>
+      <c r="B51" s="17"/>
+      <c r="C51" s="17"/>
+      <c r="D51" s="17"/>
+      <c r="E51" s="17"/>
+      <c r="F51" s="17"/>
+      <c r="G51" s="17"/>
+      <c r="H51" s="17"/>
+    </row>
+    <row r="52" spans="1:10" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="205" t="s">
         <v>13</v>
       </c>
-      <c r="B51" s="230"/>
-      <c r="C51" s="230"/>
-      <c r="D51" s="230"/>
-      <c r="E51" s="230"/>
-      <c r="F51" s="230"/>
-      <c r="G51" s="230"/>
-      <c r="H51" s="231"/>
-    </row>
-    <row r="52" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="222" t="s">
+      <c r="B52" s="206"/>
+      <c r="C52" s="206"/>
+      <c r="D52" s="206"/>
+      <c r="E52" s="206"/>
+      <c r="F52" s="206"/>
+      <c r="G52" s="206"/>
+      <c r="H52" s="207"/>
+    </row>
+    <row r="53" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="198" t="s">
         <v>137</v>
       </c>
-      <c r="B52" s="222"/>
-      <c r="C52" s="222"/>
-      <c r="D52" s="222"/>
-      <c r="E52" s="222"/>
-      <c r="F52" s="222"/>
-      <c r="G52" s="222"/>
-      <c r="H52" s="30">
-        <v>1627667.8413207317</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A53" s="25" t="s">
+      <c r="B53" s="198"/>
+      <c r="C53" s="198"/>
+      <c r="D53" s="198"/>
+      <c r="E53" s="198"/>
+      <c r="F53" s="198"/>
+      <c r="G53" s="198"/>
+      <c r="H53" s="30">
+        <v>3224697.8013207326</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" s="25" t="s">
         <v>135</v>
-      </c>
-      <c r="B53" s="26"/>
-      <c r="C53" s="26"/>
-      <c r="D53" s="26"/>
-      <c r="E53" s="26"/>
-      <c r="F53" s="26"/>
-      <c r="G53" s="26"/>
-      <c r="H53" s="32">
-        <f>Planilla!I31</f>
-        <v>2458640.5300000007</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A54" s="25" t="s">
-        <v>156</v>
       </c>
       <c r="B54" s="26"/>
       <c r="C54" s="26"/>
@@ -2899,13 +2947,14 @@
       <c r="E54" s="26"/>
       <c r="F54" s="26"/>
       <c r="G54" s="26"/>
-      <c r="H54" s="169">
-        <v>-4586</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H54" s="32">
+        <f>Planilla!I31</f>
+        <v>1223530.3999999997</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="25" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="B55" s="26"/>
       <c r="C55" s="26"/>
@@ -2913,43 +2962,55 @@
       <c r="E55" s="26"/>
       <c r="F55" s="26"/>
       <c r="G55" s="26"/>
-      <c r="H55" s="27">
-        <f>-(H38+H44)</f>
-        <v>-2119217.7999999998</v>
-      </c>
-      <c r="J55" s="14"/>
-    </row>
-    <row r="56" spans="1:10" ht="18" x14ac:dyDescent="0.35">
-      <c r="A56" s="28" t="s">
+      <c r="H55" s="168"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="B56" s="26"/>
+      <c r="C56" s="26"/>
+      <c r="D56" s="26"/>
+      <c r="E56" s="26"/>
+      <c r="F56" s="26"/>
+      <c r="G56" s="26"/>
+      <c r="H56" s="27">
+        <f>-(H39+H45)</f>
+        <v>-2116540.9200000004</v>
+      </c>
+      <c r="J56" s="14"/>
+    </row>
+    <row r="57" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A57" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="B56" s="29"/>
-      <c r="C56" s="29"/>
-      <c r="D56" s="29"/>
-      <c r="E56" s="29"/>
-      <c r="F56" s="29"/>
-      <c r="G56" s="29"/>
-      <c r="H56" s="33">
-        <f>SUM(H52:H55)</f>
-        <v>1962504.5713207326</v>
+      <c r="B57" s="29"/>
+      <c r="C57" s="29"/>
+      <c r="D57" s="29"/>
+      <c r="E57" s="29"/>
+      <c r="F57" s="29"/>
+      <c r="G57" s="29"/>
+      <c r="H57" s="33">
+        <f>SUM(H53:H56)</f>
+        <v>2331687.2813207316</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="14">
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="D6:H8"/>
-    <mergeCell ref="A47:G47"/>
-    <mergeCell ref="A52:G52"/>
-    <mergeCell ref="A40:H41"/>
-    <mergeCell ref="A51:H51"/>
+    <mergeCell ref="A48:G48"/>
+    <mergeCell ref="A53:G53"/>
+    <mergeCell ref="A41:H42"/>
+    <mergeCell ref="A52:H52"/>
     <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A24:H24"/>
-    <mergeCell ref="A31:H31"/>
-    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A32:H32"/>
+    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="A44:G44"/>
+    <mergeCell ref="A45:G45"/>
     <mergeCell ref="A43:G43"/>
-    <mergeCell ref="A44:G44"/>
-    <mergeCell ref="A42:G42"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="95" orientation="portrait" r:id="rId1"/>
@@ -2963,193 +3024,193 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:V38"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.44140625" style="34" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="11.33203125" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="12.109375" customWidth="1"/>
-    <col min="4" max="4" width="22.109375" customWidth="1"/>
-    <col min="5" max="5" width="12.33203125" customWidth="1"/>
-    <col min="6" max="6" width="6.33203125" style="36" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" style="35" customWidth="1"/>
-    <col min="8" max="8" width="7.5546875" style="35" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="14.6640625" style="35" customWidth="1"/>
-    <col min="10" max="10" width="0.44140625" style="35" customWidth="1"/>
-    <col min="11" max="11" width="11.109375" style="35" customWidth="1"/>
-    <col min="12" max="12" width="0.109375" style="35" customWidth="1"/>
-    <col min="13" max="13" width="10.33203125" customWidth="1"/>
-    <col min="14" max="14" width="12.88671875" customWidth="1"/>
-    <col min="15" max="15" width="12.109375" customWidth="1"/>
-    <col min="16" max="16" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.42578125" style="34" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" customWidth="1"/>
+    <col min="4" max="4" width="22.140625" customWidth="1"/>
+    <col min="5" max="5" width="12.28515625" customWidth="1"/>
+    <col min="6" max="6" width="6.28515625" style="36" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" style="35" customWidth="1"/>
+    <col min="8" max="8" width="7.5703125" style="35" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="35" customWidth="1"/>
+    <col min="10" max="10" width="0.42578125" style="35" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" style="35" customWidth="1"/>
+    <col min="12" max="12" width="0.140625" style="35" customWidth="1"/>
+    <col min="13" max="13" width="10.28515625" customWidth="1"/>
+    <col min="14" max="14" width="12.85546875" customWidth="1"/>
+    <col min="15" max="15" width="12.140625" customWidth="1"/>
+    <col min="16" max="16" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="9" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.33203125" customWidth="1"/>
+    <col min="18" max="18" width="13.28515625" customWidth="1"/>
     <col min="19" max="19" width="14" customWidth="1"/>
     <col min="20" max="20" width="12" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="246" t="str">
+    <row r="1" spans="1:20" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="222" t="str">
         <f>Gastos!E9</f>
         <v xml:space="preserve">PERIODO: DICIEMBRE </v>
       </c>
-      <c r="B1" s="247"/>
-      <c r="C1" s="247"/>
-      <c r="D1" s="247"/>
-      <c r="E1" s="247"/>
-      <c r="F1" s="247"/>
-      <c r="G1" s="247"/>
-      <c r="H1" s="247"/>
-      <c r="I1" s="247"/>
-      <c r="J1" s="247"/>
-      <c r="K1" s="247"/>
-      <c r="L1" s="247"/>
-      <c r="M1" s="247"/>
-      <c r="N1" s="247"/>
-      <c r="O1" s="247"/>
-      <c r="P1" s="247"/>
-      <c r="Q1" s="247"/>
-      <c r="R1" s="247"/>
-      <c r="S1" s="248"/>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="B1" s="223"/>
+      <c r="C1" s="223"/>
+      <c r="D1" s="223"/>
+      <c r="E1" s="223"/>
+      <c r="F1" s="223"/>
+      <c r="G1" s="223"/>
+      <c r="H1" s="223"/>
+      <c r="I1" s="223"/>
+      <c r="J1" s="223"/>
+      <c r="K1" s="223"/>
+      <c r="L1" s="223"/>
+      <c r="M1" s="223"/>
+      <c r="N1" s="223"/>
+      <c r="O1" s="223"/>
+      <c r="P1" s="223"/>
+      <c r="Q1" s="223"/>
+      <c r="R1" s="223"/>
+      <c r="S1" s="224"/>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="69"/>
-      <c r="C2" s="154">
-        <f>687024.57+500000</f>
-        <v>1187024.5699999998</v>
-      </c>
-      <c r="F2" s="266" t="s">
-        <v>158</v>
-      </c>
-      <c r="G2" s="267"/>
-      <c r="H2" s="267"/>
-      <c r="I2" s="267"/>
-      <c r="J2" s="267"/>
-      <c r="K2" s="268"/>
+      <c r="C2" s="153">
+        <f>687024.57+(687024.57+364820.21)</f>
+        <v>1738869.35</v>
+      </c>
+      <c r="F2" s="260" t="s">
+        <v>154</v>
+      </c>
+      <c r="G2" s="261"/>
+      <c r="H2" s="261"/>
+      <c r="I2" s="261"/>
+      <c r="J2" s="261"/>
+      <c r="K2" s="262"/>
       <c r="L2" s="12"/>
-      <c r="M2" s="256" t="s">
-        <v>150</v>
-      </c>
-      <c r="N2" s="257"/>
-      <c r="O2" s="257"/>
-      <c r="P2" s="257"/>
-      <c r="Q2" s="257"/>
-      <c r="R2" s="257"/>
-      <c r="S2" s="258"/>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="M2" s="232" t="s">
+        <v>149</v>
+      </c>
+      <c r="N2" s="233"/>
+      <c r="O2" s="233"/>
+      <c r="P2" s="233"/>
+      <c r="Q2" s="233"/>
+      <c r="R2" s="233"/>
+      <c r="S2" s="234"/>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="65"/>
-      <c r="D3" s="154">
-        <v>500000</v>
-      </c>
-      <c r="F3" s="269"/>
-      <c r="G3" s="270"/>
-      <c r="H3" s="270"/>
-      <c r="I3" s="270"/>
-      <c r="J3" s="270"/>
-      <c r="K3" s="271"/>
+      <c r="D3" s="153">
+        <v>1051844.78</v>
+      </c>
+      <c r="F3" s="263"/>
+      <c r="G3" s="264"/>
+      <c r="H3" s="264"/>
+      <c r="I3" s="264"/>
+      <c r="J3" s="264"/>
+      <c r="K3" s="265"/>
       <c r="L3" s="67"/>
-      <c r="M3" s="259"/>
-      <c r="N3" s="260"/>
-      <c r="O3" s="260"/>
-      <c r="P3" s="260"/>
-      <c r="Q3" s="260"/>
-      <c r="R3" s="260"/>
-      <c r="S3" s="261"/>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="M3" s="235"/>
+      <c r="N3" s="236"/>
+      <c r="O3" s="236"/>
+      <c r="P3" s="236"/>
+      <c r="Q3" s="236"/>
+      <c r="R3" s="236"/>
+      <c r="S3" s="237"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="65"/>
-      <c r="C4" s="265" t="s">
+      <c r="C4" s="241" t="s">
         <v>143</v>
       </c>
-      <c r="D4" s="265"/>
-      <c r="F4" s="269"/>
-      <c r="G4" s="270"/>
-      <c r="H4" s="270"/>
-      <c r="I4" s="270"/>
-      <c r="J4" s="270"/>
-      <c r="K4" s="271"/>
+      <c r="D4" s="241"/>
+      <c r="F4" s="263"/>
+      <c r="G4" s="264"/>
+      <c r="H4" s="264"/>
+      <c r="I4" s="264"/>
+      <c r="J4" s="264"/>
+      <c r="K4" s="265"/>
       <c r="L4" s="67"/>
-      <c r="M4" s="259"/>
-      <c r="N4" s="260"/>
-      <c r="O4" s="260"/>
-      <c r="P4" s="260"/>
-      <c r="Q4" s="260"/>
-      <c r="R4" s="260"/>
-      <c r="S4" s="261"/>
-    </row>
-    <row r="5" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M4" s="235"/>
+      <c r="N4" s="236"/>
+      <c r="O4" s="236"/>
+      <c r="P4" s="236"/>
+      <c r="Q4" s="236"/>
+      <c r="R4" s="236"/>
+      <c r="S4" s="237"/>
+    </row>
+    <row r="5" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="65"/>
       <c r="B5" s="68"/>
-      <c r="C5" s="254">
+      <c r="C5" s="230">
         <f>D3</f>
-        <v>500000</v>
-      </c>
-      <c r="D5" s="254"/>
+        <v>1051844.78</v>
+      </c>
+      <c r="D5" s="230"/>
       <c r="E5" s="12"/>
-      <c r="F5" s="272"/>
-      <c r="G5" s="273"/>
-      <c r="H5" s="273"/>
-      <c r="I5" s="273"/>
-      <c r="J5" s="273"/>
-      <c r="K5" s="274"/>
+      <c r="F5" s="266"/>
+      <c r="G5" s="267"/>
+      <c r="H5" s="267"/>
+      <c r="I5" s="267"/>
+      <c r="J5" s="267"/>
+      <c r="K5" s="268"/>
       <c r="L5" s="67"/>
-      <c r="M5" s="259"/>
-      <c r="N5" s="260"/>
-      <c r="O5" s="260"/>
-      <c r="P5" s="260"/>
-      <c r="Q5" s="260"/>
-      <c r="R5" s="260"/>
-      <c r="S5" s="261"/>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="M5" s="235"/>
+      <c r="N5" s="236"/>
+      <c r="O5" s="236"/>
+      <c r="P5" s="236"/>
+      <c r="Q5" s="236"/>
+      <c r="R5" s="236"/>
+      <c r="S5" s="237"/>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="65"/>
       <c r="C6" s="12" t="s">
         <v>142</v>
       </c>
       <c r="D6" s="12"/>
       <c r="E6" s="12"/>
-      <c r="F6" s="275" t="s">
-        <v>159</v>
-      </c>
-      <c r="G6" s="276"/>
-      <c r="H6" s="276"/>
-      <c r="I6" s="276"/>
-      <c r="J6" s="276"/>
-      <c r="K6" s="277"/>
+      <c r="F6" s="242" t="s">
+        <v>155</v>
+      </c>
+      <c r="G6" s="243"/>
+      <c r="H6" s="243"/>
+      <c r="I6" s="243"/>
+      <c r="J6" s="243"/>
+      <c r="K6" s="244"/>
       <c r="L6" s="37"/>
-      <c r="M6" s="259"/>
-      <c r="N6" s="260"/>
-      <c r="O6" s="260"/>
-      <c r="P6" s="260"/>
-      <c r="Q6" s="260"/>
-      <c r="R6" s="260"/>
-      <c r="S6" s="261"/>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="M6" s="235"/>
+      <c r="N6" s="236"/>
+      <c r="O6" s="236"/>
+      <c r="P6" s="236"/>
+      <c r="Q6" s="236"/>
+      <c r="R6" s="236"/>
+      <c r="S6" s="237"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="65"/>
       <c r="B7" s="64"/>
-      <c r="C7" s="254">
+      <c r="C7" s="230">
         <f>C2-D3</f>
-        <v>687024.56999999983</v>
-      </c>
-      <c r="D7" s="254"/>
+        <v>687024.57000000007</v>
+      </c>
+      <c r="D7" s="230"/>
       <c r="E7" s="66"/>
-      <c r="F7" s="278"/>
-      <c r="G7" s="279"/>
-      <c r="H7" s="279"/>
-      <c r="I7" s="279"/>
-      <c r="J7" s="279"/>
-      <c r="K7" s="280"/>
+      <c r="F7" s="245"/>
+      <c r="G7" s="246"/>
+      <c r="H7" s="246"/>
+      <c r="I7" s="246"/>
+      <c r="J7" s="246"/>
+      <c r="K7" s="247"/>
       <c r="L7" s="37"/>
-      <c r="M7" s="259"/>
-      <c r="N7" s="260"/>
-      <c r="O7" s="260"/>
-      <c r="P7" s="260"/>
-      <c r="Q7" s="260"/>
-      <c r="R7" s="260"/>
-      <c r="S7" s="261"/>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="M7" s="235"/>
+      <c r="N7" s="236"/>
+      <c r="O7" s="236"/>
+      <c r="P7" s="236"/>
+      <c r="Q7" s="236"/>
+      <c r="R7" s="236"/>
+      <c r="S7" s="237"/>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="65"/>
       <c r="B8" s="64"/>
       <c r="C8" s="64" t="s">
@@ -3157,45 +3218,45 @@
       </c>
       <c r="D8" s="64"/>
       <c r="E8" s="64"/>
-      <c r="F8" s="278"/>
-      <c r="G8" s="279"/>
-      <c r="H8" s="279"/>
-      <c r="I8" s="279"/>
-      <c r="J8" s="279"/>
-      <c r="K8" s="280"/>
+      <c r="F8" s="245"/>
+      <c r="G8" s="246"/>
+      <c r="H8" s="246"/>
+      <c r="I8" s="246"/>
+      <c r="J8" s="246"/>
+      <c r="K8" s="247"/>
       <c r="L8" s="37"/>
-      <c r="M8" s="259"/>
-      <c r="N8" s="260"/>
-      <c r="O8" s="260"/>
-      <c r="P8" s="260"/>
-      <c r="Q8" s="260"/>
-      <c r="R8" s="260"/>
-      <c r="S8" s="261"/>
-    </row>
-    <row r="9" spans="1:20" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M8" s="235"/>
+      <c r="N8" s="236"/>
+      <c r="O8" s="236"/>
+      <c r="P8" s="236"/>
+      <c r="Q8" s="236"/>
+      <c r="R8" s="236"/>
+      <c r="S8" s="237"/>
+    </row>
+    <row r="9" spans="1:20" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="63"/>
       <c r="B9" s="62"/>
-      <c r="C9" s="255">
-        <v>170000</v>
-      </c>
-      <c r="D9" s="255"/>
+      <c r="C9" s="231">
+        <v>0</v>
+      </c>
+      <c r="D9" s="231"/>
       <c r="E9" s="61"/>
-      <c r="F9" s="281"/>
-      <c r="G9" s="282"/>
-      <c r="H9" s="282"/>
-      <c r="I9" s="282"/>
-      <c r="J9" s="282"/>
-      <c r="K9" s="283"/>
+      <c r="F9" s="248"/>
+      <c r="G9" s="249"/>
+      <c r="H9" s="249"/>
+      <c r="I9" s="249"/>
+      <c r="J9" s="249"/>
+      <c r="K9" s="250"/>
       <c r="L9" s="60"/>
-      <c r="M9" s="262"/>
-      <c r="N9" s="263"/>
-      <c r="O9" s="263"/>
-      <c r="P9" s="263"/>
-      <c r="Q9" s="263"/>
-      <c r="R9" s="263"/>
-      <c r="S9" s="264"/>
-    </row>
-    <row r="10" spans="1:20" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M9" s="238"/>
+      <c r="N9" s="239"/>
+      <c r="O9" s="239"/>
+      <c r="P9" s="239"/>
+      <c r="Q9" s="239"/>
+      <c r="R9" s="239"/>
+      <c r="S9" s="240"/>
+    </row>
+    <row r="10" spans="1:20" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="59" t="s">
         <v>31</v>
       </c>
@@ -3252,32 +3313,32 @@
         <v>1ER vto - VTO: 15/01'</v>
       </c>
       <c r="S10" s="55" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="148" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="147" t="s">
         <v>68</v>
       </c>
-      <c r="B11" s="149"/>
-      <c r="C11" s="150" t="s">
+      <c r="B11" s="148"/>
+      <c r="C11" s="149" t="s">
         <v>33</v>
       </c>
-      <c r="D11" s="151" t="s">
+      <c r="D11" s="150" t="s">
         <v>87</v>
       </c>
-      <c r="E11" s="137"/>
-      <c r="F11" s="152">
+      <c r="E11" s="136"/>
+      <c r="F11" s="151">
         <v>7.9</v>
       </c>
-      <c r="G11" s="161">
-        <v>150476.01</v>
-      </c>
-      <c r="H11" s="161">
-        <v>0</v>
-      </c>
-      <c r="I11" s="164">
-        <v>154990.01</v>
+      <c r="G11" s="160">
+        <v>102556.01</v>
+      </c>
+      <c r="H11" s="160">
+        <v>0</v>
+      </c>
+      <c r="I11" s="160">
+        <v>105633</v>
       </c>
       <c r="J11" s="48" t="e">
         <f>C8*F11/100</f>
@@ -3285,175 +3346,178 @@
       </c>
       <c r="K11" s="48">
         <f t="shared" ref="K11:K18" si="0">G11-H11-I11</f>
-        <v>-4514</v>
+        <v>-3076.9900000000052</v>
       </c>
       <c r="L11" s="48"/>
-      <c r="M11" s="153">
+      <c r="M11" s="152">
         <f>(K11+L11)*3%</f>
-        <v>-135.41999999999999</v>
-      </c>
-      <c r="N11" s="153">
+        <v>-92.309700000000149</v>
+      </c>
+      <c r="N11" s="152">
         <f t="shared" ref="N11:N19" si="1">K11+M11+L11</f>
-        <v>-4649.42</v>
+        <v>-3169.2997000000055</v>
       </c>
       <c r="O11" s="48">
         <f>C$7*F11/100</f>
-        <v>54274.941029999994</v>
+        <v>54274.941030000009</v>
       </c>
       <c r="P11" s="48">
         <f>C$9*F11/100</f>
-        <v>13430</v>
+        <v>0</v>
       </c>
       <c r="Q11" s="48">
         <f>C$5*F11/100</f>
-        <v>39500</v>
-      </c>
-      <c r="R11" s="161">
+        <v>83095.737620000014</v>
+      </c>
+      <c r="R11" s="160">
         <f>ROUND(O11+N11+P11+Q11,0) + T11</f>
-        <v>102556.01</v>
-      </c>
-      <c r="S11" s="160">
+        <v>134201.01</v>
+      </c>
+      <c r="S11" s="159">
         <f>ROUND(R11+R11*3%,0) + T11</f>
-        <v>105633.01</v>
+        <v>138227.01</v>
       </c>
       <c r="T11" s="31">
         <v>0.01</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="142" t="s">
+    <row r="12" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="B12" s="135"/>
-      <c r="C12" s="143" t="s">
+      <c r="B12" s="134"/>
+      <c r="C12" s="142" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="144" t="s">
+      <c r="D12" s="143" t="s">
         <v>88</v>
       </c>
-      <c r="E12" s="145"/>
-      <c r="F12" s="146">
+      <c r="E12" s="144"/>
+      <c r="F12" s="145">
         <v>7.9</v>
       </c>
-      <c r="G12" s="164">
-        <v>150476.01999999999</v>
-      </c>
-      <c r="H12" s="164">
-        <v>0</v>
-      </c>
-      <c r="I12" s="164">
+      <c r="G12" s="163">
+        <v>107205.02</v>
+      </c>
+      <c r="H12" s="163">
+        <v>0</v>
+      </c>
+      <c r="I12" s="160">
         <f t="shared" ref="I12" si="2">G12</f>
-        <v>150476.01999999999</v>
-      </c>
-      <c r="J12" s="133" t="e">
+        <v>107205.02</v>
+      </c>
+      <c r="J12" s="132" t="e">
         <f>C8*F12/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K12" s="133">
+      <c r="K12" s="132">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L12" s="133"/>
-      <c r="M12" s="139">
+      <c r="L12" s="132"/>
+      <c r="M12" s="138">
         <f t="shared" ref="M12:M29" si="3">(K12+L12)*3%</f>
         <v>0</v>
       </c>
-      <c r="N12" s="139">
+      <c r="N12" s="138">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O12" s="133">
+      <c r="O12" s="132">
         <f t="shared" ref="O12:O29" si="4">C$7*F12/100</f>
-        <v>54274.941029999994</v>
+        <v>54274.941030000009</v>
       </c>
       <c r="P12" s="48">
         <f t="shared" ref="P12:P29" si="5">C$9*F12/100</f>
-        <v>13430</v>
+        <v>0</v>
       </c>
       <c r="Q12" s="48">
         <f t="shared" ref="Q12:Q22" si="6">C$5*F12/100</f>
-        <v>39500</v>
-      </c>
-      <c r="R12" s="161">
+        <v>83095.737620000014</v>
+      </c>
+      <c r="R12" s="160">
         <f t="shared" ref="R12:R29" si="7">ROUND(O12+N12+P12+Q12,0) + T12</f>
-        <v>107205.02</v>
-      </c>
-      <c r="S12" s="160">
+        <v>137371.01999999999</v>
+      </c>
+      <c r="S12" s="159">
         <f t="shared" ref="S12:S29" si="8">ROUND(R12+R12*3%,0) + T12</f>
-        <v>110421.02</v>
+        <v>141492.01999999999</v>
       </c>
       <c r="T12" s="31">
         <f t="shared" ref="T12:T29" si="9">T11+0.01</f>
         <v>0.02</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="134" t="s">
+    <row r="13" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="133" t="s">
         <v>70</v>
       </c>
-      <c r="B13" s="135"/>
+      <c r="B13" s="134"/>
       <c r="C13" s="71" t="s">
         <v>35</v>
       </c>
-      <c r="D13" s="136" t="s">
+      <c r="D13" s="135" t="s">
         <v>89</v>
       </c>
-      <c r="E13" s="137" t="s">
+      <c r="E13" s="136" t="s">
         <v>97</v>
       </c>
-      <c r="F13" s="138">
+      <c r="F13" s="137">
         <v>7.9</v>
       </c>
-      <c r="G13" s="161">
-        <v>150476.03</v>
-      </c>
-      <c r="H13" s="164">
-        <v>0</v>
-      </c>
-      <c r="I13" s="164"/>
-      <c r="J13" s="133" t="e">
+      <c r="G13" s="160">
+        <v>262195.03000000003</v>
+      </c>
+      <c r="H13" s="163">
+        <v>0</v>
+      </c>
+      <c r="I13" s="160">
+        <f>G13</f>
+        <v>262195.03000000003</v>
+      </c>
+      <c r="J13" s="132" t="e">
         <f>C8*F13/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K13" s="133">
+      <c r="K13" s="132">
         <f t="shared" si="0"/>
-        <v>150476.03</v>
-      </c>
-      <c r="L13" s="133"/>
-      <c r="M13" s="139">
+        <v>0</v>
+      </c>
+      <c r="L13" s="132"/>
+      <c r="M13" s="138">
         <f t="shared" si="3"/>
-        <v>4514.2808999999997</v>
-      </c>
-      <c r="N13" s="139">
+        <v>0</v>
+      </c>
+      <c r="N13" s="138">
         <f t="shared" si="1"/>
-        <v>154990.31090000001</v>
-      </c>
-      <c r="O13" s="133">
+        <v>0</v>
+      </c>
+      <c r="O13" s="132">
         <f t="shared" si="4"/>
-        <v>54274.941029999994</v>
+        <v>54274.941030000009</v>
       </c>
       <c r="P13" s="48">
         <f t="shared" si="5"/>
-        <v>13430</v>
+        <v>0</v>
       </c>
       <c r="Q13" s="48">
         <f t="shared" si="6"/>
-        <v>39500</v>
-      </c>
-      <c r="R13" s="161">
+        <v>83095.737620000014</v>
+      </c>
+      <c r="R13" s="160">
         <f t="shared" si="7"/>
-        <v>262195.03000000003</v>
-      </c>
-      <c r="S13" s="160">
+        <v>137371.03</v>
+      </c>
+      <c r="S13" s="159">
         <f t="shared" si="8"/>
-        <v>270061.03000000003</v>
+        <v>141492.03</v>
       </c>
       <c r="T13" s="31">
         <f t="shared" si="9"/>
         <v>0.03</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="85" t="s">
         <v>71</v>
       </c>
@@ -3461,19 +3525,20 @@
       <c r="C14" s="70" t="s">
         <v>36</v>
       </c>
-      <c r="D14" s="131" t="s">
+      <c r="D14" s="130" t="s">
         <v>90</v>
       </c>
-      <c r="E14" s="88"/>
+      <c r="E14" s="87"/>
       <c r="F14" s="72">
         <v>7.9</v>
       </c>
-      <c r="G14" s="165">
-        <v>150476.04</v>
-      </c>
-      <c r="H14" s="166"/>
-      <c r="I14" s="164">
-        <v>154990.04</v>
+      <c r="G14" s="164">
+        <v>102556.04</v>
+      </c>
+      <c r="H14" s="165"/>
+      <c r="I14" s="160">
+        <f>G14</f>
+        <v>102556.04</v>
       </c>
       <c r="J14" s="46" t="e">
         <f>C8*F14/100</f>
@@ -3481,853 +3546,843 @@
       </c>
       <c r="K14" s="46">
         <f t="shared" si="0"/>
-        <v>-4514</v>
+        <v>0</v>
       </c>
       <c r="L14" s="47"/>
       <c r="M14" s="45">
         <f t="shared" si="3"/>
-        <v>-135.41999999999999</v>
+        <v>0</v>
       </c>
       <c r="N14" s="45">
         <f t="shared" si="1"/>
-        <v>-4649.42</v>
+        <v>0</v>
       </c>
       <c r="O14" s="46">
         <f t="shared" si="4"/>
-        <v>54274.941029999994</v>
+        <v>54274.941030000009</v>
       </c>
       <c r="P14" s="48">
         <f t="shared" si="5"/>
-        <v>13430</v>
+        <v>0</v>
       </c>
       <c r="Q14" s="48">
         <f t="shared" si="6"/>
-        <v>39500</v>
-      </c>
-      <c r="R14" s="161">
+        <v>83095.737620000014</v>
+      </c>
+      <c r="R14" s="160">
         <f t="shared" si="7"/>
-        <v>102556.04</v>
-      </c>
-      <c r="S14" s="160">
+        <v>137371.04</v>
+      </c>
+      <c r="S14" s="159">
         <f t="shared" si="8"/>
-        <v>105633.04</v>
+        <v>141492.04</v>
       </c>
       <c r="T14" s="31">
         <f t="shared" si="9"/>
         <v>0.04</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="85" t="s">
         <v>72</v>
       </c>
       <c r="B15" s="52"/>
-      <c r="C15" s="70" t="s">
+      <c r="C15" s="71" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="86" t="s">
+      <c r="D15" s="135" t="s">
         <v>91</v>
       </c>
-      <c r="E15" s="88"/>
-      <c r="F15" s="72">
+      <c r="E15" s="136"/>
+      <c r="F15" s="137">
         <v>7.9</v>
       </c>
-      <c r="G15" s="167">
-        <v>150476.04999999999</v>
-      </c>
-      <c r="H15" s="166">
-        <v>0</v>
-      </c>
-      <c r="I15" s="164">
-        <f>154990.05</f>
-        <v>154990.04999999999</v>
-      </c>
-      <c r="J15" s="46" t="e">
+      <c r="G15" s="160">
+        <v>102556.05</v>
+      </c>
+      <c r="H15" s="270">
+        <v>0</v>
+      </c>
+      <c r="I15" s="160">
+        <f>G15</f>
+        <v>102556.05</v>
+      </c>
+      <c r="J15" s="132" t="e">
         <f>C8*F15/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K15" s="46">
+      <c r="K15" s="132">
         <f t="shared" si="0"/>
-        <v>-4514</v>
-      </c>
-      <c r="L15" s="46"/>
-      <c r="M15" s="45">
+        <v>0</v>
+      </c>
+      <c r="L15" s="132"/>
+      <c r="M15" s="138">
         <f t="shared" si="3"/>
-        <v>-135.41999999999999</v>
-      </c>
-      <c r="N15" s="45">
+        <v>0</v>
+      </c>
+      <c r="N15" s="138">
         <f t="shared" si="1"/>
-        <v>-4649.42</v>
-      </c>
-      <c r="O15" s="46">
+        <v>0</v>
+      </c>
+      <c r="O15" s="132">
         <f t="shared" si="4"/>
-        <v>54274.941029999994</v>
+        <v>54274.941030000009</v>
       </c>
       <c r="P15" s="48">
         <f t="shared" si="5"/>
-        <v>13430</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="48">
         <f t="shared" si="6"/>
-        <v>39500</v>
-      </c>
-      <c r="R15" s="161">
+        <v>83095.737620000014</v>
+      </c>
+      <c r="R15" s="160">
         <f t="shared" si="7"/>
-        <v>102556.05</v>
-      </c>
-      <c r="S15" s="160">
+        <v>137371.04999999999</v>
+      </c>
+      <c r="S15" s="159">
         <f t="shared" si="8"/>
-        <v>105633.05</v>
+        <v>141492.04999999999</v>
       </c>
       <c r="T15" s="31">
         <f t="shared" si="9"/>
         <v>0.05</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="134" t="s">
+    <row r="16" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="133" t="s">
         <v>73</v>
       </c>
-      <c r="B16" s="135"/>
-      <c r="C16" s="172" t="s">
+      <c r="B16" s="134"/>
+      <c r="C16" s="71" t="s">
         <v>38</v>
       </c>
-      <c r="D16" s="173" t="s">
+      <c r="D16" s="135" t="s">
         <v>144</v>
       </c>
-      <c r="E16" s="174" t="s">
-        <v>149</v>
-      </c>
-      <c r="F16" s="175">
+      <c r="E16" s="136" t="s">
+        <v>148</v>
+      </c>
+      <c r="F16" s="137">
         <v>7.9</v>
       </c>
-      <c r="G16" s="176">
-        <v>150476.06</v>
-      </c>
-      <c r="H16" s="177">
-        <v>0</v>
-      </c>
-      <c r="I16" s="177">
-        <f>163345-I28</f>
-        <v>152748.82</v>
-      </c>
-      <c r="J16" s="178" t="e">
+      <c r="G16" s="160">
+        <v>108010.06</v>
+      </c>
+      <c r="H16" s="163">
+        <v>0</v>
+      </c>
+      <c r="I16" s="160">
+        <v>104864.06</v>
+      </c>
+      <c r="J16" s="132" t="e">
         <f>C8*F16/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K16" s="178">
+      <c r="K16" s="132">
         <f t="shared" si="0"/>
-        <v>-2272.7600000000093</v>
-      </c>
-      <c r="L16" s="178"/>
-      <c r="M16" s="179">
+        <v>3146</v>
+      </c>
+      <c r="L16" s="132"/>
+      <c r="M16" s="138">
         <f t="shared" si="3"/>
-        <v>-68.18280000000027</v>
-      </c>
-      <c r="N16" s="179">
+        <v>94.38</v>
+      </c>
+      <c r="N16" s="138">
         <f t="shared" si="1"/>
-        <v>-2340.9428000000098</v>
-      </c>
-      <c r="O16" s="178">
+        <v>3240.38</v>
+      </c>
+      <c r="O16" s="132">
         <f t="shared" si="4"/>
-        <v>54274.941029999994</v>
-      </c>
-      <c r="P16" s="180">
+        <v>54274.941030000009</v>
+      </c>
+      <c r="P16" s="48">
         <f t="shared" si="5"/>
-        <v>13430</v>
-      </c>
-      <c r="Q16" s="180">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="48">
         <f t="shared" si="6"/>
-        <v>39500</v>
-      </c>
-      <c r="R16" s="176">
+        <v>83095.737620000014</v>
+      </c>
+      <c r="R16" s="160">
         <f t="shared" si="7"/>
-        <v>104864.06</v>
-      </c>
-      <c r="S16" s="181">
+        <v>140611.06</v>
+      </c>
+      <c r="S16" s="159">
         <f t="shared" si="8"/>
-        <v>108010.06</v>
+        <v>144829.06</v>
       </c>
       <c r="T16" s="31">
         <f t="shared" si="9"/>
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="85" t="s">
         <v>74</v>
       </c>
       <c r="B17" s="52"/>
-      <c r="C17" s="172" t="s">
+      <c r="C17" s="71" t="s">
         <v>39</v>
       </c>
-      <c r="D17" s="173" t="s">
+      <c r="D17" s="135" t="s">
         <v>92</v>
       </c>
-      <c r="E17" s="174" t="s">
+      <c r="E17" s="136" t="s">
         <v>132</v>
       </c>
-      <c r="F17" s="175">
+      <c r="F17" s="137">
         <v>7.9</v>
       </c>
-      <c r="G17" s="176">
-        <v>161167.07</v>
-      </c>
-      <c r="H17" s="177">
-        <v>0</v>
-      </c>
-      <c r="I17" s="177">
-        <f>176916.2-I23</f>
-        <v>166320.07</v>
-      </c>
-      <c r="J17" s="178" t="e">
+      <c r="G17" s="160">
+        <v>101897.07</v>
+      </c>
+      <c r="H17" s="163">
+        <v>0</v>
+      </c>
+      <c r="I17" s="160">
+        <f>G17</f>
+        <v>101897.07</v>
+      </c>
+      <c r="J17" s="132" t="e">
         <f>C8*F17/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K17" s="178">
+      <c r="K17" s="132">
         <f t="shared" si="0"/>
-        <v>-5153</v>
-      </c>
-      <c r="L17" s="178"/>
-      <c r="M17" s="179">
+        <v>0</v>
+      </c>
+      <c r="L17" s="132"/>
+      <c r="M17" s="138">
         <f t="shared" si="3"/>
-        <v>-154.59</v>
-      </c>
-      <c r="N17" s="179">
+        <v>0</v>
+      </c>
+      <c r="N17" s="138">
         <f t="shared" si="1"/>
-        <v>-5307.59</v>
-      </c>
-      <c r="O17" s="178">
+        <v>0</v>
+      </c>
+      <c r="O17" s="132">
         <f t="shared" si="4"/>
-        <v>54274.941029999994</v>
-      </c>
-      <c r="P17" s="180">
+        <v>54274.941030000009</v>
+      </c>
+      <c r="P17" s="48">
         <f t="shared" si="5"/>
-        <v>13430</v>
-      </c>
-      <c r="Q17" s="180">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="48">
         <f t="shared" si="6"/>
-        <v>39500</v>
-      </c>
-      <c r="R17" s="176">
+        <v>83095.737620000014</v>
+      </c>
+      <c r="R17" s="160">
         <f t="shared" si="7"/>
-        <v>101897.07</v>
-      </c>
-      <c r="S17" s="181">
+        <v>137371.07</v>
+      </c>
+      <c r="S17" s="159">
         <f t="shared" si="8"/>
-        <v>104954.07</v>
+        <v>141492.07</v>
       </c>
       <c r="T17" s="31">
         <f t="shared" si="9"/>
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="134" t="s">
+    <row r="18" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="133" t="s">
         <v>75</v>
       </c>
-      <c r="B18" s="135"/>
+      <c r="B18" s="134"/>
       <c r="C18" s="71" t="s">
         <v>40</v>
       </c>
-      <c r="D18" s="136" t="s">
+      <c r="D18" s="135" t="s">
         <v>134</v>
       </c>
-      <c r="E18" s="137" t="s">
+      <c r="E18" s="136" t="s">
         <v>133</v>
       </c>
-      <c r="F18" s="138">
+      <c r="F18" s="137">
         <v>7.9</v>
       </c>
-      <c r="G18" s="161">
-        <v>308030.08000000002</v>
-      </c>
-      <c r="H18" s="164">
-        <v>0</v>
-      </c>
-      <c r="I18" s="164">
-        <f>G18</f>
-        <v>308030.08000000002</v>
-      </c>
-      <c r="J18" s="133" t="e">
+      <c r="G18" s="160">
+        <v>107205.08</v>
+      </c>
+      <c r="H18" s="163">
+        <v>0</v>
+      </c>
+      <c r="I18" s="160"/>
+      <c r="J18" s="132" t="e">
         <f>C8*F18/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K18" s="133">
+      <c r="K18" s="132">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L18" s="133"/>
-      <c r="M18" s="139">
+        <v>107205.08</v>
+      </c>
+      <c r="L18" s="132"/>
+      <c r="M18" s="138">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N18" s="139">
+        <v>3216.1523999999999</v>
+      </c>
+      <c r="N18" s="138">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="O18" s="133">
+        <v>110421.23240000001</v>
+      </c>
+      <c r="O18" s="132">
         <f t="shared" si="4"/>
-        <v>54274.941029999994</v>
+        <v>54274.941030000009</v>
       </c>
       <c r="P18" s="48">
         <f t="shared" si="5"/>
-        <v>13430</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="48">
         <f t="shared" si="6"/>
-        <v>39500</v>
-      </c>
-      <c r="R18" s="161">
+        <v>83095.737620000014</v>
+      </c>
+      <c r="R18" s="160">
         <f t="shared" si="7"/>
-        <v>107205.08</v>
-      </c>
-      <c r="S18" s="160">
+        <v>247792.08</v>
+      </c>
+      <c r="S18" s="159">
         <f t="shared" si="8"/>
-        <v>110421.08</v>
+        <v>255226.08</v>
       </c>
       <c r="T18" s="31">
         <f t="shared" si="9"/>
         <v>0.08</v>
       </c>
     </row>
-    <row r="19" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="134" t="s">
+    <row r="19" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="133" t="s">
         <v>76</v>
       </c>
-      <c r="B19" s="135"/>
+      <c r="B19" s="134"/>
       <c r="C19" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="D19" s="136" t="s">
+      <c r="D19" s="135" t="s">
         <v>93</v>
       </c>
-      <c r="E19" s="137"/>
-      <c r="F19" s="138">
+      <c r="E19" s="136"/>
+      <c r="F19" s="137">
         <v>7.9</v>
       </c>
-      <c r="G19" s="161">
-        <v>150476.09</v>
-      </c>
-      <c r="H19" s="164">
-        <v>0</v>
-      </c>
-      <c r="I19" s="164">
-        <v>154990.09</v>
-      </c>
-      <c r="J19" s="133" t="e">
+      <c r="G19" s="160">
+        <v>97906.09</v>
+      </c>
+      <c r="H19" s="163">
+        <v>0</v>
+      </c>
+      <c r="I19" s="160">
+        <f>G19</f>
+        <v>97906.09</v>
+      </c>
+      <c r="J19" s="132" t="e">
         <f>C8*F19/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K19" s="133">
+      <c r="K19" s="132">
         <f t="shared" ref="K19:K29" si="10">G19-H19-I19</f>
-        <v>-4514</v>
-      </c>
-      <c r="L19" s="133">
+        <v>0</v>
+      </c>
+      <c r="L19" s="132">
         <f>G19-I19</f>
-        <v>-4514</v>
-      </c>
-      <c r="M19" s="139">
+        <v>0</v>
+      </c>
+      <c r="M19" s="138">
         <f t="shared" si="3"/>
-        <v>-270.83999999999997</v>
-      </c>
-      <c r="N19" s="139">
+        <v>0</v>
+      </c>
+      <c r="N19" s="138">
         <f t="shared" si="1"/>
-        <v>-9298.84</v>
-      </c>
-      <c r="O19" s="133">
+        <v>0</v>
+      </c>
+      <c r="O19" s="132">
         <f t="shared" si="4"/>
-        <v>54274.941029999994</v>
+        <v>54274.941030000009</v>
       </c>
       <c r="P19" s="48">
         <f t="shared" si="5"/>
-        <v>13430</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="48">
         <f t="shared" si="6"/>
-        <v>39500</v>
-      </c>
-      <c r="R19" s="161">
+        <v>83095.737620000014</v>
+      </c>
+      <c r="R19" s="160">
         <f t="shared" si="7"/>
-        <v>97906.09</v>
-      </c>
-      <c r="S19" s="160">
+        <v>137371.09</v>
+      </c>
+      <c r="S19" s="159">
         <f t="shared" si="8"/>
-        <v>100843.09</v>
+        <v>141492.09</v>
       </c>
       <c r="T19" s="31">
         <f t="shared" si="9"/>
         <v>0.09</v>
       </c>
     </row>
-    <row r="20" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="170" t="s">
+    <row r="20" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="169" t="s">
         <v>77</v>
       </c>
-      <c r="B20" s="135"/>
-      <c r="C20" s="172" t="s">
+      <c r="B20" s="134"/>
+      <c r="C20" s="170" t="s">
         <v>42</v>
       </c>
-      <c r="D20" s="173" t="s">
+      <c r="D20" s="171" t="s">
         <v>94</v>
       </c>
-      <c r="E20" s="174"/>
-      <c r="F20" s="175">
+      <c r="E20" s="172"/>
+      <c r="F20" s="173">
         <v>7.9</v>
       </c>
-      <c r="G20" s="176">
-        <v>308030.09999999998</v>
-      </c>
-      <c r="H20" s="177"/>
-      <c r="I20" s="177">
-        <f>142126+165904.25</f>
-        <v>308030.25</v>
-      </c>
-      <c r="J20" s="178"/>
-      <c r="K20" s="178">
+      <c r="G20" s="174">
+        <v>107205.1</v>
+      </c>
+      <c r="H20" s="175"/>
+      <c r="I20" s="174">
+        <f>113547.25-I25</f>
+        <v>107205.1</v>
+      </c>
+      <c r="J20" s="176"/>
+      <c r="K20" s="176">
         <f t="shared" si="10"/>
-        <v>-0.15000000002328306</v>
-      </c>
-      <c r="L20" s="178"/>
-      <c r="M20" s="179">
+        <v>0</v>
+      </c>
+      <c r="L20" s="176"/>
+      <c r="M20" s="177">
         <f t="shared" si="3"/>
-        <v>-4.5000000006984921E-3</v>
-      </c>
-      <c r="N20" s="179">
+        <v>0</v>
+      </c>
+      <c r="N20" s="177">
         <f t="shared" ref="N20:N29" si="11">K20+M20+L20</f>
-        <v>-0.15450000002398157</v>
-      </c>
-      <c r="O20" s="178">
+        <v>0</v>
+      </c>
+      <c r="O20" s="176">
         <f t="shared" si="4"/>
-        <v>54274.941029999994</v>
-      </c>
-      <c r="P20" s="180">
+        <v>54274.941030000009</v>
+      </c>
+      <c r="P20" s="178">
         <f t="shared" si="5"/>
-        <v>13430</v>
-      </c>
-      <c r="Q20" s="180">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="178">
         <f t="shared" si="6"/>
-        <v>39500</v>
-      </c>
-      <c r="R20" s="176">
+        <v>83095.737620000014</v>
+      </c>
+      <c r="R20" s="174">
         <f t="shared" si="7"/>
-        <v>107205.1</v>
-      </c>
-      <c r="S20" s="181">
+        <v>137371.1</v>
+      </c>
+      <c r="S20" s="179">
         <f t="shared" si="8"/>
-        <v>110421.1</v>
-      </c>
-      <c r="T20" s="163">
+        <v>141492.1</v>
+      </c>
+      <c r="T20" s="162">
         <f t="shared" si="9"/>
         <v>9.9999999999999992E-2</v>
       </c>
       <c r="U20" s="13"/>
     </row>
-    <row r="21" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="170" t="s">
+    <row r="21" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="169" t="s">
         <v>78</v>
       </c>
-      <c r="B21" s="135"/>
-      <c r="C21" s="172" t="s">
+      <c r="B21" s="134"/>
+      <c r="C21" s="71" t="s">
         <v>43</v>
       </c>
-      <c r="D21" s="173" t="s">
+      <c r="D21" s="135" t="s">
         <v>95</v>
       </c>
-      <c r="E21" s="174" t="s">
+      <c r="E21" s="136" t="s">
         <v>98</v>
       </c>
-      <c r="F21" s="175">
+      <c r="F21" s="137">
         <v>7.9</v>
       </c>
-      <c r="G21" s="176">
-        <v>308030.11</v>
-      </c>
-      <c r="H21" s="177"/>
-      <c r="I21" s="177">
-        <f>339197-I24</f>
-        <v>317909.86</v>
-      </c>
-      <c r="J21" s="178"/>
-      <c r="K21" s="178">
+      <c r="G21" s="160">
+        <v>97029.11</v>
+      </c>
+      <c r="H21" s="163"/>
+      <c r="I21" s="160"/>
+      <c r="J21" s="132"/>
+      <c r="K21" s="132">
         <f t="shared" si="10"/>
-        <v>-9879.75</v>
-      </c>
-      <c r="L21" s="178"/>
-      <c r="M21" s="179">
+        <v>97029.11</v>
+      </c>
+      <c r="L21" s="132"/>
+      <c r="M21" s="138">
         <f t="shared" si="3"/>
-        <v>-296.39249999999998</v>
-      </c>
-      <c r="N21" s="179">
+        <v>2910.8732999999997</v>
+      </c>
+      <c r="N21" s="138">
         <f t="shared" si="11"/>
-        <v>-10176.1425</v>
-      </c>
-      <c r="O21" s="178">
+        <v>99939.983300000007</v>
+      </c>
+      <c r="O21" s="132">
         <f t="shared" si="4"/>
-        <v>54274.941029999994</v>
-      </c>
-      <c r="P21" s="180">
+        <v>54274.941030000009</v>
+      </c>
+      <c r="P21" s="48">
         <f t="shared" si="5"/>
-        <v>13430</v>
-      </c>
-      <c r="Q21" s="180">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="48">
         <f t="shared" si="6"/>
-        <v>39500</v>
-      </c>
-      <c r="R21" s="176">
+        <v>83095.737620000014</v>
+      </c>
+      <c r="R21" s="160">
         <f t="shared" si="7"/>
-        <v>97029.11</v>
-      </c>
-      <c r="S21" s="181">
+        <v>237311.11</v>
+      </c>
+      <c r="S21" s="159">
         <f t="shared" si="8"/>
-        <v>99940.11</v>
+        <v>244430.11</v>
       </c>
       <c r="T21" s="31">
         <f t="shared" si="9"/>
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="22" spans="1:22" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="170" t="s">
+    <row r="22" spans="1:22" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="133" t="s">
         <v>79</v>
       </c>
-      <c r="B22" s="171"/>
-      <c r="C22" s="172" t="s">
+      <c r="B22" s="134"/>
+      <c r="C22" s="71" t="s">
         <v>44</v>
       </c>
-      <c r="D22" s="173" t="s">
+      <c r="D22" s="135" t="s">
         <v>139</v>
       </c>
-      <c r="E22" s="174" t="s">
+      <c r="E22" s="136" t="s">
         <v>138</v>
       </c>
-      <c r="F22" s="175">
+      <c r="F22" s="137">
         <v>7.9</v>
       </c>
-      <c r="G22" s="176">
-        <v>308030.12</v>
-      </c>
-      <c r="H22" s="177"/>
-      <c r="I22" s="177">
-        <f>339197.31-I29</f>
-        <v>317910.12</v>
-      </c>
-      <c r="J22" s="178"/>
-      <c r="K22" s="178">
+      <c r="G22" s="160">
+        <v>99940.12</v>
+      </c>
+      <c r="H22" s="163"/>
+      <c r="I22" s="160">
+        <f>106472.31-I29</f>
+        <v>99940.12</v>
+      </c>
+      <c r="J22" s="132"/>
+      <c r="K22" s="132">
         <f t="shared" si="10"/>
-        <v>-9880</v>
-      </c>
-      <c r="L22" s="178"/>
-      <c r="M22" s="179">
+        <v>0</v>
+      </c>
+      <c r="L22" s="132"/>
+      <c r="M22" s="138">
         <f t="shared" si="3"/>
-        <v>-296.39999999999998</v>
-      </c>
-      <c r="N22" s="179">
+        <v>0</v>
+      </c>
+      <c r="N22" s="138">
         <f t="shared" si="11"/>
-        <v>-10176.4</v>
-      </c>
-      <c r="O22" s="178">
+        <v>0</v>
+      </c>
+      <c r="O22" s="132">
         <f t="shared" si="4"/>
-        <v>54274.941029999994</v>
-      </c>
-      <c r="P22" s="180">
+        <v>54274.941030000009</v>
+      </c>
+      <c r="P22" s="48">
         <f t="shared" si="5"/>
-        <v>13430</v>
-      </c>
-      <c r="Q22" s="180">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="48">
         <f t="shared" si="6"/>
-        <v>39500</v>
-      </c>
-      <c r="R22" s="176">
+        <v>83095.737620000014</v>
+      </c>
+      <c r="R22" s="160">
         <f t="shared" si="7"/>
-        <v>97029.119999999995</v>
-      </c>
-      <c r="S22" s="181">
+        <v>137371.12</v>
+      </c>
+      <c r="S22" s="159">
         <f t="shared" si="8"/>
-        <v>99940.12</v>
+        <v>141492.12</v>
       </c>
       <c r="T22" s="31">
         <f t="shared" si="9"/>
         <v>0.11999999999999998</v>
       </c>
-    </row>
-    <row r="23" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="85"/>
-      <c r="B23" s="52"/>
-      <c r="C23" s="172" t="s">
+      <c r="V22" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="133"/>
+      <c r="B23" s="134"/>
+      <c r="C23" s="71" t="s">
         <v>80</v>
       </c>
-      <c r="D23" s="182" t="str">
+      <c r="D23" s="139" t="str">
         <f>D17</f>
         <v>Estevez Norberto Omar</v>
       </c>
-      <c r="E23" s="174" t="s">
+      <c r="E23" s="136" t="s">
         <v>132</v>
       </c>
-      <c r="F23" s="175">
+      <c r="F23" s="137">
         <v>0.74</v>
       </c>
-      <c r="G23" s="176">
-        <v>10596.13</v>
-      </c>
-      <c r="H23" s="177"/>
-      <c r="I23" s="177">
+      <c r="G23" s="160">
+        <v>6342.13</v>
+      </c>
+      <c r="H23" s="163"/>
+      <c r="I23" s="160">
         <f>G23</f>
-        <v>10596.13</v>
-      </c>
-      <c r="J23" s="178"/>
-      <c r="K23" s="178">
+        <v>6342.13</v>
+      </c>
+      <c r="J23" s="132"/>
+      <c r="K23" s="132">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="L23" s="178"/>
-      <c r="M23" s="179">
+      <c r="L23" s="132"/>
+      <c r="M23" s="138">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N23" s="179">
+      <c r="N23" s="138">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="O23" s="178">
+      <c r="O23" s="132">
         <f t="shared" si="4"/>
-        <v>5083.9818179999984</v>
-      </c>
-      <c r="P23" s="180">
+        <v>5083.9818180000002</v>
+      </c>
+      <c r="P23" s="48">
         <f t="shared" si="5"/>
-        <v>1258</v>
-      </c>
-      <c r="Q23" s="178"/>
-      <c r="R23" s="176">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="132"/>
+      <c r="R23" s="160">
         <f t="shared" si="7"/>
-        <v>6342.13</v>
-      </c>
-      <c r="S23" s="181">
+        <v>5084.13</v>
+      </c>
+      <c r="S23" s="159">
         <f t="shared" si="8"/>
-        <v>6532.13</v>
+        <v>5237.13</v>
       </c>
       <c r="T23" s="31">
         <f t="shared" si="9"/>
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="24" spans="1:22" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="170"/>
-      <c r="B24" s="135"/>
-      <c r="C24" s="172" t="s">
+    <row r="24" spans="1:22" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="169"/>
+      <c r="B24" s="134"/>
+      <c r="C24" s="71" t="s">
         <v>81</v>
       </c>
-      <c r="D24" s="182" t="str">
+      <c r="D24" s="139" t="str">
         <f>D21</f>
         <v>Moro Vanesa Yania / Juan Carlos Moro</v>
       </c>
-      <c r="E24" s="174" t="s">
+      <c r="E24" s="136" t="s">
         <v>98</v>
       </c>
-      <c r="F24" s="175">
+      <c r="F24" s="137">
         <v>0.74</v>
       </c>
-      <c r="G24" s="176">
-        <v>21287.14</v>
-      </c>
-      <c r="H24" s="177"/>
-      <c r="I24" s="177">
-        <f>G24</f>
-        <v>21287.14</v>
-      </c>
-      <c r="J24" s="178"/>
-      <c r="K24" s="178">
+      <c r="G24" s="160">
+        <v>6342.14</v>
+      </c>
+      <c r="H24" s="163"/>
+      <c r="I24" s="160"/>
+      <c r="J24" s="132"/>
+      <c r="K24" s="132">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="L24" s="178"/>
-      <c r="M24" s="179">
+        <v>6342.14</v>
+      </c>
+      <c r="L24" s="132"/>
+      <c r="M24" s="138">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N24" s="179">
+        <v>190.26420000000002</v>
+      </c>
+      <c r="N24" s="138">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="O24" s="178">
+        <v>6532.4041999999999</v>
+      </c>
+      <c r="O24" s="132">
         <f t="shared" si="4"/>
-        <v>5083.9818179999984</v>
-      </c>
-      <c r="P24" s="180">
+        <v>5083.9818180000002</v>
+      </c>
+      <c r="P24" s="48">
         <f t="shared" si="5"/>
-        <v>1258</v>
-      </c>
-      <c r="Q24" s="178">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="132">
         <f>'Calculo Servicios  (2)'!H22</f>
         <v>0</v>
       </c>
-      <c r="R24" s="176">
+      <c r="R24" s="160">
         <f t="shared" si="7"/>
-        <v>6342.14</v>
-      </c>
-      <c r="S24" s="181">
+        <v>11616.14</v>
+      </c>
+      <c r="S24" s="159">
         <f t="shared" si="8"/>
-        <v>6532.14</v>
+        <v>11965.14</v>
       </c>
       <c r="T24" s="31">
         <f t="shared" si="9"/>
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="85"/>
-      <c r="B25" s="52"/>
-      <c r="C25" s="208" t="s">
+    <row r="25" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="133"/>
+      <c r="B25" s="134"/>
+      <c r="C25" s="71" t="s">
         <v>82</v>
       </c>
-      <c r="D25" s="209" t="str">
+      <c r="D25" s="139" t="str">
         <f>D20</f>
         <v>Scarlercio Jorge Omar</v>
       </c>
-      <c r="E25" s="209"/>
-      <c r="F25" s="210">
+      <c r="E25" s="139"/>
+      <c r="F25" s="137">
         <v>0.74</v>
       </c>
-      <c r="G25" s="211">
-        <v>21287.15</v>
-      </c>
-      <c r="H25" s="212"/>
-      <c r="I25" s="212">
+      <c r="G25" s="160">
+        <v>6342.15</v>
+      </c>
+      <c r="H25" s="163"/>
+      <c r="I25" s="160">
         <f>G25</f>
-        <v>21287.15</v>
-      </c>
-      <c r="J25" s="213"/>
-      <c r="K25" s="213">
+        <v>6342.15</v>
+      </c>
+      <c r="J25" s="132"/>
+      <c r="K25" s="132">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="L25" s="213"/>
-      <c r="M25" s="214">
+      <c r="L25" s="132"/>
+      <c r="M25" s="138">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N25" s="214">
+      <c r="N25" s="138">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="O25" s="213">
+      <c r="O25" s="132">
         <f t="shared" si="4"/>
-        <v>5083.9818179999984</v>
-      </c>
-      <c r="P25" s="215">
+        <v>5083.9818180000002</v>
+      </c>
+      <c r="P25" s="48">
         <f t="shared" si="5"/>
-        <v>1258</v>
-      </c>
-      <c r="Q25" s="213">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="132">
         <f>'Calculo Servicios  (2)'!H23</f>
         <v>0</v>
       </c>
-      <c r="R25" s="211">
+      <c r="R25" s="160">
         <f t="shared" si="7"/>
-        <v>6342.15</v>
-      </c>
-      <c r="S25" s="216">
+        <v>5084.1499999999996</v>
+      </c>
+      <c r="S25" s="159">
         <f t="shared" si="8"/>
-        <v>6532.15</v>
-      </c>
-      <c r="T25" s="31">
+        <v>5237.1499999999996</v>
+      </c>
+      <c r="T25" s="269">
         <f t="shared" si="9"/>
         <v>0.15</v>
       </c>
-      <c r="U25" s="217" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="134"/>
-      <c r="B26" s="132"/>
+      <c r="U25" s="13"/>
+    </row>
+    <row r="26" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="133"/>
+      <c r="B26" s="131"/>
       <c r="C26" s="71" t="s">
         <v>83</v>
       </c>
-      <c r="D26" s="140" t="str">
+      <c r="D26" s="139" t="str">
         <f>D18</f>
         <v>Lopez Gabriela</v>
       </c>
-      <c r="E26" s="137" t="s">
+      <c r="E26" s="136" t="s">
         <v>133</v>
       </c>
-      <c r="F26" s="138">
+      <c r="F26" s="137">
         <v>0.74</v>
       </c>
-      <c r="G26" s="161">
-        <v>21287.16</v>
-      </c>
-      <c r="H26" s="164">
-        <v>0</v>
-      </c>
-      <c r="I26" s="164">
-        <f>G26</f>
-        <v>21287.16</v>
-      </c>
-      <c r="J26" s="133" t="e">
+      <c r="G26" s="160">
+        <v>6342.16</v>
+      </c>
+      <c r="H26" s="163">
+        <v>0</v>
+      </c>
+      <c r="I26" s="160"/>
+      <c r="J26" s="132" t="e">
         <f>C8*F26/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K26" s="133">
+      <c r="K26" s="132">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="L26" s="133"/>
-      <c r="M26" s="139">
+        <v>6342.16</v>
+      </c>
+      <c r="L26" s="132"/>
+      <c r="M26" s="138">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N26" s="139">
+        <v>190.26479999999998</v>
+      </c>
+      <c r="N26" s="138">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="O26" s="133">
+        <v>6532.4247999999998</v>
+      </c>
+      <c r="O26" s="132">
         <f t="shared" si="4"/>
-        <v>5083.9818179999984</v>
+        <v>5083.9818180000002</v>
       </c>
       <c r="P26" s="48">
         <f t="shared" si="5"/>
-        <v>1258</v>
-      </c>
-      <c r="Q26" s="133">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="132">
         <f>'Calculo Servicios  (2)'!H24</f>
         <v>0</v>
       </c>
-      <c r="R26" s="161">
+      <c r="R26" s="160">
         <f t="shared" si="7"/>
-        <v>6342.16</v>
-      </c>
-      <c r="S26" s="160">
+        <v>11616.16</v>
+      </c>
+      <c r="S26" s="159">
         <f t="shared" si="8"/>
-        <v>6532.16</v>
+        <v>11965.16</v>
       </c>
       <c r="T26" s="31">
         <f t="shared" si="9"/>
         <v>0.16</v>
       </c>
     </row>
-    <row r="27" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="85"/>
       <c r="B27" s="52"/>
       <c r="C27" s="70" t="s">
         <v>84</v>
       </c>
-      <c r="D27" s="87" t="str">
+      <c r="D27" s="86" t="str">
         <f>D15</f>
         <v>Cecilia Mariel Cassettari</v>
       </c>
-      <c r="E27" s="87"/>
+      <c r="E27" s="86"/>
       <c r="F27" s="72">
         <v>0.74</v>
       </c>
-      <c r="G27" s="167">
-        <v>10596.17</v>
-      </c>
-      <c r="H27" s="168">
-        <v>0</v>
-      </c>
-      <c r="I27" s="164">
-        <v>10914.17</v>
+      <c r="G27" s="166">
+        <v>6014.17</v>
+      </c>
+      <c r="H27" s="167">
+        <v>0</v>
+      </c>
+      <c r="I27" s="160">
+        <f>G27</f>
+        <v>6014.17</v>
       </c>
       <c r="J27" s="46" t="e">
         <f>C8*F27/100</f>
@@ -4335,178 +4390,177 @@
       </c>
       <c r="K27" s="46">
         <f t="shared" si="10"/>
-        <v>-318</v>
+        <v>0</v>
       </c>
       <c r="L27" s="46"/>
       <c r="M27" s="45">
         <f t="shared" si="3"/>
-        <v>-9.5399999999999991</v>
+        <v>0</v>
       </c>
       <c r="N27" s="45">
         <f t="shared" si="11"/>
-        <v>-327.54000000000002</v>
+        <v>0</v>
       </c>
       <c r="O27" s="46">
         <f t="shared" si="4"/>
-        <v>5083.9818179999984</v>
+        <v>5083.9818180000002</v>
       </c>
       <c r="P27" s="48">
         <f t="shared" si="5"/>
-        <v>1258</v>
+        <v>0</v>
       </c>
       <c r="Q27" s="46">
         <f>'Calculo Servicios  (2)'!H25</f>
         <v>0</v>
       </c>
-      <c r="R27" s="161">
+      <c r="R27" s="160">
         <f t="shared" si="7"/>
-        <v>6014.17</v>
-      </c>
-      <c r="S27" s="160">
+        <v>5084.17</v>
+      </c>
+      <c r="S27" s="159">
         <f t="shared" si="8"/>
-        <v>6195.17</v>
+        <v>5237.17</v>
       </c>
       <c r="T27" s="31">
         <f t="shared" si="9"/>
         <v>0.17</v>
       </c>
     </row>
-    <row r="28" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="155"/>
-      <c r="B28" s="156"/>
-      <c r="C28" s="172" t="s">
+    <row r="28" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="154"/>
+      <c r="B28" s="155"/>
+      <c r="C28" s="71" t="s">
         <v>85</v>
       </c>
-      <c r="D28" s="182" t="str">
+      <c r="D28" s="139" t="str">
         <f>D16</f>
         <v>Perez Sebastian</v>
       </c>
-      <c r="E28" s="174" t="s">
-        <v>149</v>
-      </c>
-      <c r="F28" s="183">
+      <c r="E28" s="136" t="s">
+        <v>148</v>
+      </c>
+      <c r="F28" s="271">
         <v>0.74</v>
       </c>
-      <c r="G28" s="176">
-        <v>10596.18</v>
-      </c>
-      <c r="H28" s="176">
-        <v>0</v>
-      </c>
-      <c r="I28" s="177">
-        <f>G28</f>
-        <v>10596.18</v>
-      </c>
-      <c r="J28" s="180">
-        <v>0</v>
-      </c>
-      <c r="K28" s="180">
+      <c r="G28" s="160">
+        <v>6532.18</v>
+      </c>
+      <c r="H28" s="160">
+        <v>0</v>
+      </c>
+      <c r="I28" s="160">
+        <v>6342.18</v>
+      </c>
+      <c r="J28" s="48">
+        <v>0</v>
+      </c>
+      <c r="K28" s="48">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="L28" s="180"/>
-      <c r="M28" s="184">
+        <v>190</v>
+      </c>
+      <c r="L28" s="48"/>
+      <c r="M28" s="152">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N28" s="184">
+        <v>5.7</v>
+      </c>
+      <c r="N28" s="152">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="O28" s="180">
+        <v>195.7</v>
+      </c>
+      <c r="O28" s="48">
         <f t="shared" si="4"/>
-        <v>5083.9818179999984</v>
-      </c>
-      <c r="P28" s="180">
+        <v>5083.9818180000002</v>
+      </c>
+      <c r="P28" s="48">
         <f t="shared" si="5"/>
-        <v>1258</v>
-      </c>
-      <c r="Q28" s="180">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="48">
         <f>'Calculo Servicios  (2)'!H26</f>
         <v>0</v>
       </c>
-      <c r="R28" s="176">
+      <c r="R28" s="160">
         <f t="shared" si="7"/>
-        <v>6342.18</v>
-      </c>
-      <c r="S28" s="181">
+        <v>5280.18</v>
+      </c>
+      <c r="S28" s="159">
         <f t="shared" si="8"/>
-        <v>6532.18</v>
+        <v>5439.18</v>
       </c>
       <c r="T28" s="31">
         <f t="shared" si="9"/>
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="29" spans="1:22" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="134"/>
-      <c r="B29" s="147"/>
-      <c r="C29" s="172" t="s">
+    <row r="29" spans="1:22" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="133"/>
+      <c r="B29" s="146"/>
+      <c r="C29" s="71" t="s">
         <v>86</v>
       </c>
-      <c r="D29" s="182" t="str">
+      <c r="D29" s="139" t="str">
         <f>D22</f>
         <v>Rodriguez Flavio/Rodriguez Mauro</v>
       </c>
-      <c r="E29" s="174" t="s">
+      <c r="E29" s="136" t="s">
         <v>138</v>
       </c>
-      <c r="F29" s="185">
+      <c r="F29" s="272">
         <v>0.74</v>
       </c>
-      <c r="G29" s="176">
-        <v>21287.19</v>
-      </c>
-      <c r="H29" s="177">
-        <v>0</v>
-      </c>
-      <c r="I29" s="177">
+      <c r="G29" s="160">
+        <v>6532.19</v>
+      </c>
+      <c r="H29" s="163">
+        <v>0</v>
+      </c>
+      <c r="I29" s="160">
         <f>G29</f>
-        <v>21287.19</v>
-      </c>
-      <c r="J29" s="178" t="e">
+        <v>6532.19</v>
+      </c>
+      <c r="J29" s="132" t="e">
         <f>C8*F29/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K29" s="178">
+      <c r="K29" s="132">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="L29" s="178"/>
-      <c r="M29" s="179">
+      <c r="L29" s="132"/>
+      <c r="M29" s="138">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N29" s="179">
+      <c r="N29" s="138">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="O29" s="178">
+      <c r="O29" s="132">
         <f t="shared" si="4"/>
-        <v>5083.9818179999984</v>
-      </c>
-      <c r="P29" s="180">
+        <v>5083.9818180000002</v>
+      </c>
+      <c r="P29" s="48">
         <f t="shared" si="5"/>
-        <v>1258</v>
-      </c>
-      <c r="Q29" s="178">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="132">
         <f>'Calculo Servicios  (2)'!H27</f>
         <v>0</v>
       </c>
-      <c r="R29" s="176">
+      <c r="R29" s="160">
         <f t="shared" si="7"/>
-        <v>6342.19</v>
-      </c>
-      <c r="S29" s="181">
+        <v>5084.1899999999996</v>
+      </c>
+      <c r="S29" s="159">
         <f t="shared" si="8"/>
-        <v>6532.19</v>
+        <v>5237.1899999999996</v>
       </c>
       <c r="T29" s="31">
         <f t="shared" si="9"/>
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="30" spans="1:22" ht="21" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:22" ht="21" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="53"/>
       <c r="B30" s="52"/>
       <c r="C30" s="51"/>
@@ -4532,16 +4586,16 @@
       <c r="R30" s="47"/>
       <c r="S30" s="84"/>
     </row>
-    <row r="31" spans="1:22" s="39" customFormat="1" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="252"/>
-      <c r="B31" s="253"/>
-      <c r="C31" s="253"/>
+    <row r="31" spans="1:22" s="39" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="228"/>
+      <c r="B31" s="229"/>
+      <c r="C31" s="229"/>
       <c r="D31" s="44"/>
       <c r="E31" s="44"/>
       <c r="F31" s="73"/>
       <c r="G31" s="42">
         <f>SUM(G11:G30)</f>
-        <v>2563556.9000000004</v>
+        <v>1440707.8999999997</v>
       </c>
       <c r="H31" s="42">
         <f>SUM(H11:H30)</f>
@@ -4549,12 +4603,12 @@
       </c>
       <c r="I31" s="43">
         <f>SUM(I11:I30)</f>
-        <v>2458640.5300000007</v>
+        <v>1223530.3999999997</v>
       </c>
       <c r="J31" s="42"/>
       <c r="K31" s="43">
         <f>SUM(K11:K30)</f>
-        <v>104916.36999999997</v>
+        <v>217177.50000000003</v>
       </c>
       <c r="L31" s="42"/>
       <c r="M31" s="41"/>
@@ -4565,45 +4619,45 @@
       </c>
       <c r="P31" s="43">
         <f>SUM(P11:P29)</f>
-        <v>169966</v>
+        <v>0</v>
       </c>
       <c r="Q31" s="43">
         <f>SUM(Q11:Q29)</f>
-        <v>474000</v>
+        <v>997148.85144000023</v>
       </c>
       <c r="R31" s="43">
         <f>SUM(R11:R29)</f>
-        <v>1434270.8999999997</v>
+        <v>1907732.9000000001</v>
       </c>
       <c r="S31" s="43">
         <f>SUM(S11:S29)</f>
-        <v>1477298.8999999997</v>
+        <v>1964966.9000000001</v>
       </c>
       <c r="V31"/>
     </row>
-    <row r="32" spans="1:22" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="249" t="s">
+    <row r="32" spans="1:22" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="225" t="s">
         <v>19</v>
       </c>
-      <c r="C32" s="250"/>
-      <c r="D32" s="250"/>
-      <c r="E32" s="250"/>
-      <c r="F32" s="250"/>
-      <c r="G32" s="250"/>
-      <c r="H32" s="250"/>
-      <c r="I32" s="250"/>
-      <c r="J32" s="250"/>
-      <c r="K32" s="250"/>
-      <c r="L32" s="250"/>
-      <c r="M32" s="250"/>
-      <c r="N32" s="250"/>
-      <c r="O32" s="250"/>
-      <c r="P32" s="250"/>
-      <c r="Q32" s="250"/>
-      <c r="R32" s="250"/>
-      <c r="S32" s="251"/>
-    </row>
-    <row r="33" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C32" s="226"/>
+      <c r="D32" s="226"/>
+      <c r="E32" s="226"/>
+      <c r="F32" s="226"/>
+      <c r="G32" s="226"/>
+      <c r="H32" s="226"/>
+      <c r="I32" s="226"/>
+      <c r="J32" s="226"/>
+      <c r="K32" s="226"/>
+      <c r="L32" s="226"/>
+      <c r="M32" s="226"/>
+      <c r="N32" s="226"/>
+      <c r="O32" s="226"/>
+      <c r="P32" s="226"/>
+      <c r="Q32" s="226"/>
+      <c r="R32" s="226"/>
+      <c r="S32" s="227"/>
+    </row>
+    <row r="33" spans="3:15" x14ac:dyDescent="0.25">
       <c r="F33" s="38"/>
       <c r="G33" s="37"/>
       <c r="H33" s="37"/>
@@ -4614,80 +4668,80 @@
       </c>
       <c r="L33" s="37"/>
     </row>
-    <row r="34" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C34" s="245"/>
-      <c r="D34" s="245"/>
-      <c r="E34" s="245"/>
-      <c r="F34" s="245"/>
-      <c r="G34" s="245"/>
-      <c r="H34" s="245"/>
-      <c r="I34" s="245"/>
-      <c r="J34" s="245"/>
-      <c r="K34" s="245"/>
-      <c r="L34" s="245"/>
-      <c r="M34" s="245"/>
-      <c r="N34" s="245"/>
-      <c r="O34" s="245"/>
-    </row>
-    <row r="35" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C35" s="245"/>
-      <c r="D35" s="245"/>
-      <c r="E35" s="245"/>
-      <c r="F35" s="245"/>
-      <c r="G35" s="245"/>
-      <c r="H35" s="245"/>
-      <c r="I35" s="245"/>
-      <c r="J35" s="245"/>
-      <c r="K35" s="245"/>
-      <c r="L35" s="245"/>
-      <c r="M35" s="245"/>
-      <c r="N35" s="245"/>
-      <c r="O35" s="245"/>
-    </row>
-    <row r="36" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C36" s="245"/>
-      <c r="D36" s="245"/>
-      <c r="E36" s="245"/>
-      <c r="F36" s="245"/>
-      <c r="G36" s="245"/>
-      <c r="H36" s="245"/>
-      <c r="I36" s="245"/>
-      <c r="J36" s="245"/>
-      <c r="K36" s="245"/>
-      <c r="L36" s="245"/>
-      <c r="M36" s="245"/>
-      <c r="N36" s="245"/>
-      <c r="O36" s="245"/>
-    </row>
-    <row r="37" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C37" s="245"/>
-      <c r="D37" s="245"/>
-      <c r="E37" s="245"/>
-      <c r="F37" s="245"/>
-      <c r="G37" s="245"/>
-      <c r="H37" s="245"/>
-      <c r="I37" s="245"/>
-      <c r="J37" s="245"/>
-      <c r="K37" s="245"/>
-      <c r="L37" s="245"/>
-      <c r="M37" s="245"/>
-      <c r="N37" s="245"/>
-      <c r="O37" s="245"/>
-    </row>
-    <row r="38" spans="3:15" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C38" s="245"/>
-      <c r="D38" s="245"/>
-      <c r="E38" s="245"/>
-      <c r="F38" s="245"/>
-      <c r="G38" s="245"/>
-      <c r="H38" s="245"/>
-      <c r="I38" s="245"/>
-      <c r="J38" s="245"/>
-      <c r="K38" s="245"/>
-      <c r="L38" s="245"/>
-      <c r="M38" s="245"/>
-      <c r="N38" s="245"/>
-      <c r="O38" s="245"/>
+    <row r="34" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="C34" s="221"/>
+      <c r="D34" s="221"/>
+      <c r="E34" s="221"/>
+      <c r="F34" s="221"/>
+      <c r="G34" s="221"/>
+      <c r="H34" s="221"/>
+      <c r="I34" s="221"/>
+      <c r="J34" s="221"/>
+      <c r="K34" s="221"/>
+      <c r="L34" s="221"/>
+      <c r="M34" s="221"/>
+      <c r="N34" s="221"/>
+      <c r="O34" s="221"/>
+    </row>
+    <row r="35" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="C35" s="221"/>
+      <c r="D35" s="221"/>
+      <c r="E35" s="221"/>
+      <c r="F35" s="221"/>
+      <c r="G35" s="221"/>
+      <c r="H35" s="221"/>
+      <c r="I35" s="221"/>
+      <c r="J35" s="221"/>
+      <c r="K35" s="221"/>
+      <c r="L35" s="221"/>
+      <c r="M35" s="221"/>
+      <c r="N35" s="221"/>
+      <c r="O35" s="221"/>
+    </row>
+    <row r="36" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="C36" s="221"/>
+      <c r="D36" s="221"/>
+      <c r="E36" s="221"/>
+      <c r="F36" s="221"/>
+      <c r="G36" s="221"/>
+      <c r="H36" s="221"/>
+      <c r="I36" s="221"/>
+      <c r="J36" s="221"/>
+      <c r="K36" s="221"/>
+      <c r="L36" s="221"/>
+      <c r="M36" s="221"/>
+      <c r="N36" s="221"/>
+      <c r="O36" s="221"/>
+    </row>
+    <row r="37" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="C37" s="221"/>
+      <c r="D37" s="221"/>
+      <c r="E37" s="221"/>
+      <c r="F37" s="221"/>
+      <c r="G37" s="221"/>
+      <c r="H37" s="221"/>
+      <c r="I37" s="221"/>
+      <c r="J37" s="221"/>
+      <c r="K37" s="221"/>
+      <c r="L37" s="221"/>
+      <c r="M37" s="221"/>
+      <c r="N37" s="221"/>
+      <c r="O37" s="221"/>
+    </row>
+    <row r="38" spans="3:15" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C38" s="221"/>
+      <c r="D38" s="221"/>
+      <c r="E38" s="221"/>
+      <c r="F38" s="221"/>
+      <c r="G38" s="221"/>
+      <c r="H38" s="221"/>
+      <c r="I38" s="221"/>
+      <c r="J38" s="221"/>
+      <c r="K38" s="221"/>
+      <c r="L38" s="221"/>
+      <c r="M38" s="221"/>
+      <c r="N38" s="221"/>
+      <c r="O38" s="221"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -4704,155 +4758,155 @@
     <mergeCell ref="F6:K9"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="64" fitToWidth="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup scale="69" fitToWidth="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:O47"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.109375" style="89" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.33203125" style="89" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.109375" style="89" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.109375" style="89" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" style="89" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13.44140625" style="89" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14" style="89" bestFit="1" customWidth="1"/>
-    <col min="9" max="12" width="11.44140625" style="89"/>
-    <col min="13" max="13" width="14.6640625" style="89" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.5546875" style="89" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="11.44140625" style="89"/>
+    <col min="1" max="1" width="12.140625" style="88" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" style="88" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" style="88" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" style="88" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" style="88" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13.42578125" style="88" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14" style="88" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="11.42578125" style="88"/>
+    <col min="13" max="13" width="14.7109375" style="88" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.5703125" style="88" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="11.42578125" style="88"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="284" t="s">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A1" s="251" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="285"/>
-      <c r="C1" s="285"/>
-      <c r="D1" s="285"/>
-      <c r="E1" s="286"/>
-    </row>
-    <row r="2" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="130"/>
-      <c r="B2" s="115"/>
-      <c r="C2" s="115"/>
-      <c r="D2" s="129" t="s">
+      <c r="B1" s="252"/>
+      <c r="C1" s="252"/>
+      <c r="D1" s="252"/>
+      <c r="E1" s="253"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A2" s="129"/>
+      <c r="B2" s="114"/>
+      <c r="C2" s="114"/>
+      <c r="D2" s="128" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="126"/>
-    </row>
-    <row r="3" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="128">
+      <c r="E2" s="125"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A3" s="127">
         <f>13+28+19</f>
         <v>60</v>
       </c>
       <c r="B3" s="83">
         <v>10531.71</v>
       </c>
-      <c r="C3" s="127">
+      <c r="C3" s="126">
         <f>+B3/A3</f>
         <v>175.52849999999998</v>
       </c>
-      <c r="D3" s="127">
+      <c r="D3" s="126">
         <v>4863.8999999999996</v>
       </c>
-      <c r="E3" s="126" t="s">
+      <c r="E3" s="125" t="s">
         <v>127</v>
       </c>
-      <c r="I3" s="89" t="s">
+      <c r="I3" s="88" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="125"/>
-      <c r="B4" s="124"/>
-      <c r="C4" s="124"/>
-      <c r="D4" s="124"/>
-      <c r="E4" s="123"/>
-    </row>
-    <row r="5" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="122"/>
-      <c r="B5" s="122"/>
-      <c r="C5" s="122"/>
-      <c r="D5" s="122"/>
-      <c r="E5" s="122"/>
-    </row>
-    <row r="6" spans="1:15" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="122"/>
-      <c r="B6" s="122"/>
-      <c r="C6" s="122"/>
-      <c r="D6" s="122"/>
-      <c r="E6" s="122"/>
-    </row>
-    <row r="7" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="287" t="s">
+    <row r="4" spans="1:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="124"/>
+      <c r="B4" s="123"/>
+      <c r="C4" s="123"/>
+      <c r="D4" s="123"/>
+      <c r="E4" s="122"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A5" s="121"/>
+      <c r="B5" s="121"/>
+      <c r="C5" s="121"/>
+      <c r="D5" s="121"/>
+      <c r="E5" s="121"/>
+    </row>
+    <row r="6" spans="1:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="121"/>
+      <c r="B6" s="121"/>
+      <c r="C6" s="121"/>
+      <c r="D6" s="121"/>
+      <c r="E6" s="121"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A7" s="254" t="s">
         <v>64</v>
       </c>
-      <c r="B7" s="288"/>
-      <c r="C7" s="288"/>
-      <c r="D7" s="288"/>
-      <c r="E7" s="288"/>
-      <c r="F7" s="288"/>
-      <c r="G7" s="288"/>
-      <c r="H7" s="289"/>
-      <c r="L7" s="89" t="s">
+      <c r="B7" s="255"/>
+      <c r="C7" s="255"/>
+      <c r="D7" s="255"/>
+      <c r="E7" s="255"/>
+      <c r="F7" s="255"/>
+      <c r="G7" s="255"/>
+      <c r="H7" s="256"/>
+      <c r="L7" s="88" t="s">
         <v>59</v>
       </c>
-      <c r="M7" s="89" t="s">
+      <c r="M7" s="88" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="82">
         <v>400523.88</v>
       </c>
-      <c r="B8" s="120" t="s">
+      <c r="B8" s="119" t="s">
         <v>62</v>
       </c>
-      <c r="C8" s="120" t="s">
+      <c r="C8" s="119" t="s">
         <v>61</v>
       </c>
-      <c r="D8" s="120" t="s">
+      <c r="D8" s="119" t="s">
         <v>60</v>
       </c>
-      <c r="E8" s="121">
+      <c r="E8" s="120">
         <f>3935/2</f>
         <v>1967.5</v>
       </c>
-      <c r="F8" s="120" t="s">
+      <c r="F8" s="119" t="s">
         <v>59</v>
       </c>
-      <c r="G8" s="120" t="s">
+      <c r="G8" s="119" t="s">
         <v>58</v>
       </c>
-      <c r="H8" s="119" t="s">
+      <c r="H8" s="118" t="s">
         <v>57</v>
       </c>
-      <c r="K8" s="115">
+      <c r="K8" s="114">
         <v>19</v>
       </c>
-      <c r="L8" s="101">
+      <c r="L8" s="100">
         <v>7502.93</v>
       </c>
-      <c r="M8" s="101">
+      <c r="M8" s="100">
         <v>2365.2600000000002</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="118" t="s">
+    <row r="9" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A9" s="117" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="115">
+      <c r="B9" s="114">
         <v>1617</v>
       </c>
-      <c r="C9" s="115">
+      <c r="C9" s="114">
         <f>B9+J25</f>
         <v>1689</v>
       </c>
-      <c r="D9" s="115">
+      <c r="D9" s="114">
         <f t="shared" ref="D9:D20" si="0">+C9-B9</f>
         <v>72</v>
       </c>
@@ -4872,36 +4926,36 @@
         <f>+G9+F9</f>
         <v>24606.517913595933</v>
       </c>
-      <c r="K9" s="89">
+      <c r="K9" s="88">
         <v>106</v>
       </c>
-      <c r="L9" s="101">
+      <c r="L9" s="100">
         <f>+L8*O9</f>
         <v>1575.6152999999999</v>
       </c>
-      <c r="M9" s="89">
+      <c r="M9" s="88">
         <f>M8*21%</f>
         <v>496.70460000000003</v>
       </c>
-      <c r="N9" s="89" t="s">
+      <c r="N9" s="88" t="s">
         <v>56</v>
       </c>
       <c r="O9" s="81">
         <v>0.21</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="116" t="s">
+    <row r="10" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A10" s="115" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="115">
+      <c r="B10" s="114">
         <v>4104</v>
       </c>
-      <c r="C10" s="115">
+      <c r="C10" s="114">
         <f t="shared" ref="C10:C20" si="1">B10+J26</f>
         <v>4195</v>
       </c>
-      <c r="D10" s="115">
+      <c r="D10" s="114">
         <f t="shared" si="0"/>
         <v>91</v>
       </c>
@@ -4921,36 +4975,36 @@
         <f>+G10+F10</f>
         <v>28474.346996188055</v>
       </c>
-      <c r="K10" s="89">
+      <c r="K10" s="88">
         <v>60</v>
       </c>
-      <c r="L10" s="101">
+      <c r="L10" s="100">
         <f>+L8*O10</f>
         <v>481.98822320000005</v>
       </c>
-      <c r="M10" s="89">
+      <c r="M10" s="88">
         <f>+M8*6.424%</f>
         <v>151.94430240000003</v>
       </c>
-      <c r="N10" s="89" t="s">
+      <c r="N10" s="88" t="s">
         <v>55</v>
       </c>
       <c r="O10" s="80">
         <v>6.4240000000000005E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="116" t="s">
+    <row r="11" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A11" s="115" t="s">
         <v>35</v>
       </c>
-      <c r="B11" s="115">
+      <c r="B11" s="114">
         <v>7644</v>
       </c>
-      <c r="C11" s="115">
+      <c r="C11" s="114">
         <f t="shared" si="1"/>
         <v>7807</v>
       </c>
-      <c r="D11" s="115">
+      <c r="D11" s="114">
         <f t="shared" si="0"/>
         <v>163</v>
       </c>
@@ -4970,35 +5024,35 @@
         <f>+G11+F11</f>
         <v>43131.383519695039</v>
       </c>
-      <c r="K11" s="89">
+      <c r="K11" s="88">
         <v>79</v>
       </c>
-      <c r="L11" s="101">
+      <c r="L11" s="100">
         <f>+L8*0.001%</f>
         <v>7.5029300000000007E-2</v>
       </c>
-      <c r="M11" s="89">
+      <c r="M11" s="88">
         <v>0.03</v>
       </c>
-      <c r="N11" s="89" t="s">
+      <c r="N11" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="O11" s="101">
+      <c r="O11" s="100">
         <v>0.1</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="116" t="s">
+    <row r="12" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A12" s="115" t="s">
         <v>36</v>
       </c>
-      <c r="B12" s="115">
+      <c r="B12" s="114">
         <v>6554</v>
       </c>
-      <c r="C12" s="115">
+      <c r="C12" s="114">
         <f t="shared" si="1"/>
         <v>6730</v>
       </c>
-      <c r="D12" s="115">
+      <c r="D12" s="114">
         <f t="shared" si="0"/>
         <v>176</v>
       </c>
@@ -5018,34 +5072,34 @@
         <f t="shared" ref="H12:H20" si="2">SUM(F12:G12)</f>
         <v>45777.792891994919</v>
       </c>
-      <c r="K12" s="89">
+      <c r="K12" s="88">
         <v>89</v>
       </c>
-      <c r="L12" s="101">
+      <c r="L12" s="100">
         <v>400</v>
       </c>
-      <c r="M12" s="89">
+      <c r="M12" s="88">
         <v>253</v>
       </c>
-      <c r="N12" s="89" t="s">
+      <c r="N12" s="88" t="s">
         <v>53</v>
       </c>
-      <c r="O12" s="89">
+      <c r="O12" s="88">
         <v>653</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A13" s="116" t="s">
+    <row r="13" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A13" s="115" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="115">
+      <c r="B13" s="114">
         <v>7564</v>
       </c>
-      <c r="C13" s="115">
+      <c r="C13" s="114">
         <f t="shared" si="1"/>
         <v>7767</v>
       </c>
-      <c r="D13" s="115">
+      <c r="D13" s="114">
         <f t="shared" si="0"/>
         <v>203</v>
       </c>
@@ -5065,30 +5119,30 @@
         <f t="shared" si="2"/>
         <v>51274.181588310035</v>
       </c>
-      <c r="K13" s="89">
+      <c r="K13" s="88">
         <v>140</v>
       </c>
-      <c r="L13" s="117">
+      <c r="L13" s="116">
         <f>SUM(L8:L12)-0.45</f>
         <v>9960.1585524999991</v>
       </c>
-      <c r="M13" s="89">
+      <c r="M13" s="88">
         <f>SUM(M8:M12)</f>
         <v>3266.9389024000006</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A14" s="116" t="s">
+    <row r="14" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A14" s="115" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="115">
+      <c r="B14" s="114">
         <v>10119</v>
       </c>
-      <c r="C14" s="115">
+      <c r="C14" s="114">
         <f t="shared" si="1"/>
         <v>10334</v>
       </c>
-      <c r="D14" s="115">
+      <c r="D14" s="114">
         <f t="shared" si="0"/>
         <v>215</v>
       </c>
@@ -5108,22 +5162,22 @@
         <f t="shared" si="2"/>
         <v>53717.021008894531</v>
       </c>
-      <c r="K14" s="89">
+      <c r="K14" s="88">
         <v>143</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="116" t="s">
+    <row r="15" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A15" s="115" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="115">
+      <c r="B15" s="114">
         <v>8986</v>
       </c>
-      <c r="C15" s="115">
+      <c r="C15" s="114">
         <f t="shared" si="1"/>
         <v>9068</v>
       </c>
-      <c r="D15" s="115">
+      <c r="D15" s="114">
         <f t="shared" si="0"/>
         <v>82</v>
       </c>
@@ -5143,26 +5197,26 @@
         <f t="shared" si="2"/>
         <v>26642.217430749683</v>
       </c>
-      <c r="K15" s="89">
+      <c r="K15" s="88">
         <v>221</v>
       </c>
-      <c r="L15" s="89">
+      <c r="L15" s="88">
         <f>+L13+M13</f>
         <v>13227.0974549</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A16" s="116" t="s">
+    <row r="16" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A16" s="115" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="115">
+      <c r="B16" s="114">
         <v>7032</v>
       </c>
-      <c r="C16" s="115">
+      <c r="C16" s="114">
         <f t="shared" si="1"/>
         <v>7034</v>
       </c>
-      <c r="D16" s="115">
+      <c r="D16" s="114">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -5182,22 +5236,22 @@
         <f t="shared" si="2"/>
         <v>10356.621293519693</v>
       </c>
-      <c r="K16" s="89">
+      <c r="K16" s="88">
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="116" t="s">
+    <row r="17" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="A17" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="115">
+      <c r="B17" s="114">
         <v>1623</v>
       </c>
-      <c r="C17" s="115">
+      <c r="C17" s="114">
         <f t="shared" si="1"/>
         <v>1668</v>
       </c>
-      <c r="D17" s="115">
+      <c r="D17" s="114">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
@@ -5217,22 +5271,22 @@
         <f t="shared" si="2"/>
         <v>19110.12921728081</v>
       </c>
-      <c r="K17" s="89">
+      <c r="K17" s="88">
         <v>80</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A18" s="116" t="s">
+    <row r="18" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="A18" s="115" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="115">
+      <c r="B18" s="114">
         <v>3932</v>
       </c>
-      <c r="C18" s="115">
+      <c r="C18" s="114">
         <f t="shared" si="1"/>
         <v>4021</v>
       </c>
-      <c r="D18" s="115">
+      <c r="D18" s="114">
         <f t="shared" si="0"/>
         <v>89</v>
       </c>
@@ -5252,22 +5306,22 @@
         <f t="shared" si="2"/>
         <v>28067.2070927573</v>
       </c>
-      <c r="K18" s="89">
+      <c r="K18" s="88">
         <v>113</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A19" s="116" t="s">
+    <row r="19" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="A19" s="115" t="s">
         <v>43</v>
       </c>
-      <c r="B19" s="115">
+      <c r="B19" s="114">
         <v>6887</v>
       </c>
-      <c r="C19" s="115">
+      <c r="C19" s="114">
         <f t="shared" si="1"/>
         <v>6994</v>
       </c>
-      <c r="D19" s="115">
+      <c r="D19" s="114">
         <f t="shared" si="0"/>
         <v>107</v>
       </c>
@@ -5287,22 +5341,22 @@
         <f t="shared" si="2"/>
         <v>31731.466223634052</v>
       </c>
-      <c r="K19" s="89">
+      <c r="K19" s="88">
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A20" s="116" t="s">
+    <row r="20" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="A20" s="115" t="s">
         <v>44</v>
       </c>
-      <c r="B20" s="115">
+      <c r="B20" s="114">
         <v>1884</v>
       </c>
-      <c r="C20" s="115">
+      <c r="C20" s="114">
         <f t="shared" si="1"/>
         <v>2020</v>
       </c>
-      <c r="D20" s="115">
+      <c r="D20" s="114">
         <f t="shared" si="0"/>
         <v>136</v>
       </c>
@@ -5323,97 +5377,97 @@
         <v>37634.994823379922</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="114" t="s">
+    <row r="21" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="113" t="s">
         <v>126</v>
       </c>
-      <c r="B21" s="113"/>
-      <c r="C21" s="113"/>
-      <c r="D21" s="112">
+      <c r="B21" s="112"/>
+      <c r="C21" s="112"/>
+      <c r="D21" s="111">
         <f>SUM(D9:D20)</f>
         <v>1381</v>
       </c>
-      <c r="E21" s="111"/>
-      <c r="F21" s="91"/>
-      <c r="G21" s="91"/>
+      <c r="E21" s="110"/>
+      <c r="F21" s="90"/>
+      <c r="G21" s="90"/>
       <c r="H21" s="76">
         <f>SUM(H9:H20)</f>
         <v>400523.88</v>
       </c>
-      <c r="J21" s="101">
+      <c r="J21" s="100">
         <f>+H21-A8</f>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22" s="75">
         <f>+D21/E8</f>
         <v>0.70190597204574334</v>
       </c>
-      <c r="B22" s="110" t="s">
+      <c r="B22" s="109" t="s">
         <v>52</v>
       </c>
-      <c r="L22" s="109"/>
-    </row>
-    <row r="23" spans="1:13" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L22" s="108"/>
+    </row>
+    <row r="23" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="74">
         <f>100%-A22</f>
         <v>0.29809402795425666</v>
       </c>
-      <c r="B23" s="108" t="s">
+      <c r="B23" s="107" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A25" s="107"/>
-      <c r="J25" s="89">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A25" s="106"/>
+      <c r="J25" s="88">
         <v>72</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="J26" s="89">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="J26" s="88">
         <v>91</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="J27" s="89">
+    <row r="27" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="J27" s="88">
         <v>163</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B28" s="290" t="s">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B28" s="257" t="s">
         <v>125</v>
       </c>
-      <c r="C28" s="291"/>
-      <c r="D28" s="291"/>
-      <c r="E28" s="291"/>
-      <c r="F28" s="292"/>
-      <c r="J28" s="89">
+      <c r="C28" s="258"/>
+      <c r="D28" s="258"/>
+      <c r="E28" s="258"/>
+      <c r="F28" s="259"/>
+      <c r="J28" s="88">
         <v>176</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B29" s="106" t="s">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B29" s="105" t="s">
         <v>124</v>
       </c>
-      <c r="C29" s="105" t="s">
+      <c r="C29" s="104" t="s">
         <v>123</v>
       </c>
-      <c r="D29" s="105" t="s">
+      <c r="D29" s="104" t="s">
         <v>122</v>
       </c>
-      <c r="E29" s="105" t="s">
+      <c r="E29" s="104" t="s">
         <v>121</v>
       </c>
-      <c r="F29" s="104" t="s">
+      <c r="F29" s="103" t="s">
         <v>120</v>
       </c>
-      <c r="J29" s="89">
+      <c r="J29" s="88">
         <v>203</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B30" s="100" t="s">
+    <row r="30" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="B30" s="99" t="s">
         <v>119</v>
       </c>
       <c r="C30" s="78">
@@ -5422,21 +5476,21 @@
       <c r="D30" s="78">
         <v>0</v>
       </c>
-      <c r="E30" s="98"/>
+      <c r="E30" s="97"/>
       <c r="F30" s="77">
         <f>+C30</f>
         <v>4000</v>
       </c>
-      <c r="J30" s="103">
+      <c r="J30" s="102">
         <v>215</v>
       </c>
-      <c r="M30" s="89">
+      <c r="M30" s="88">
         <f>+H21-A8</f>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B31" s="100" t="s">
+    <row r="31" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="B31" s="99" t="s">
         <v>118</v>
       </c>
       <c r="C31" s="78">
@@ -5445,17 +5499,17 @@
       <c r="D31" s="78">
         <v>0</v>
       </c>
-      <c r="E31" s="98"/>
+      <c r="E31" s="97"/>
       <c r="F31" s="77">
         <f t="shared" ref="F31:F44" si="3">+F30+C31-D31</f>
         <v>8000</v>
       </c>
-      <c r="J31" s="89">
+      <c r="J31" s="88">
         <v>82</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B32" s="100" t="s">
+    <row r="32" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="B32" s="99" t="s">
         <v>117</v>
       </c>
       <c r="C32" s="78">
@@ -5464,17 +5518,17 @@
       <c r="D32" s="78">
         <v>0</v>
       </c>
-      <c r="E32" s="98"/>
+      <c r="E32" s="97"/>
       <c r="F32" s="77">
         <f t="shared" si="3"/>
         <v>12000</v>
       </c>
-      <c r="J32" s="89">
+      <c r="J32" s="88">
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B33" s="100" t="s">
+    <row r="33" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="B33" s="99" t="s">
         <v>116</v>
       </c>
       <c r="C33" s="78">
@@ -5483,21 +5537,21 @@
       <c r="D33" s="78">
         <v>0</v>
       </c>
-      <c r="E33" s="98"/>
+      <c r="E33" s="97"/>
       <c r="F33" s="77">
         <f t="shared" si="3"/>
         <v>16000</v>
       </c>
-      <c r="J33" s="89">
+      <c r="J33" s="88">
         <v>45</v>
       </c>
-      <c r="K33" s="102">
+      <c r="K33" s="101">
         <f>11934.02-11933.71</f>
         <v>0.31000000000130967</v>
       </c>
     </row>
-    <row r="34" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B34" s="100" t="s">
+    <row r="34" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="B34" s="99" t="s">
         <v>115</v>
       </c>
       <c r="C34" s="78">
@@ -5506,17 +5560,17 @@
       <c r="D34" s="78">
         <v>0</v>
       </c>
-      <c r="E34" s="98"/>
+      <c r="E34" s="97"/>
       <c r="F34" s="77">
         <f t="shared" si="3"/>
         <v>20000</v>
       </c>
-      <c r="J34" s="89">
+      <c r="J34" s="88">
         <v>89</v>
       </c>
     </row>
-    <row r="35" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B35" s="100" t="s">
+    <row r="35" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="B35" s="99" t="s">
         <v>114</v>
       </c>
       <c r="C35" s="78">
@@ -5525,17 +5579,17 @@
       <c r="D35" s="78">
         <v>0</v>
       </c>
-      <c r="E35" s="98"/>
+      <c r="E35" s="97"/>
       <c r="F35" s="77">
         <f t="shared" si="3"/>
         <v>24000</v>
       </c>
-      <c r="J35" s="89">
+      <c r="J35" s="88">
         <v>107</v>
       </c>
     </row>
-    <row r="36" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B36" s="100" t="s">
+    <row r="36" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="B36" s="99" t="s">
         <v>113</v>
       </c>
       <c r="C36" s="78">
@@ -5544,176 +5598,176 @@
       <c r="D36" s="78">
         <v>0</v>
       </c>
-      <c r="E36" s="98"/>
+      <c r="E36" s="97"/>
       <c r="F36" s="77">
         <f t="shared" si="3"/>
         <v>28000</v>
       </c>
-      <c r="J36" s="89">
+      <c r="J36" s="88">
         <v>136</v>
       </c>
     </row>
-    <row r="37" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B37" s="100" t="s">
+    <row r="37" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="B37" s="99" t="s">
         <v>112</v>
       </c>
-      <c r="C37" s="99">
+      <c r="C37" s="98">
         <v>4000</v>
       </c>
       <c r="D37" s="78">
         <v>0</v>
       </c>
-      <c r="E37" s="98"/>
+      <c r="E37" s="97"/>
       <c r="F37" s="77">
         <f t="shared" si="3"/>
         <v>32000</v>
       </c>
     </row>
-    <row r="38" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B38" s="100" t="s">
+    <row r="38" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="B38" s="99" t="s">
         <v>111</v>
       </c>
-      <c r="C38" s="99">
+      <c r="C38" s="98">
         <v>4000</v>
       </c>
-      <c r="D38" s="99">
+      <c r="D38" s="98">
         <v>3500</v>
       </c>
-      <c r="E38" s="98" t="s">
+      <c r="E38" s="97" t="s">
         <v>110</v>
       </c>
       <c r="F38" s="77">
         <f t="shared" si="3"/>
         <v>32500</v>
       </c>
-      <c r="M38" s="101">
+      <c r="M38" s="100">
         <f>88.05-100</f>
         <v>-11.950000000000003</v>
       </c>
     </row>
-    <row r="39" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B39" s="100" t="s">
+    <row r="39" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="B39" s="99" t="s">
         <v>109</v>
       </c>
-      <c r="C39" s="99">
+      <c r="C39" s="98">
         <v>4000</v>
       </c>
-      <c r="D39" s="98"/>
-      <c r="E39" s="98"/>
+      <c r="D39" s="97"/>
+      <c r="E39" s="97"/>
       <c r="F39" s="77">
         <f t="shared" si="3"/>
         <v>36500</v>
       </c>
     </row>
-    <row r="40" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B40" s="100" t="s">
+    <row r="40" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="B40" s="99" t="s">
         <v>108</v>
       </c>
-      <c r="C40" s="99">
+      <c r="C40" s="98">
         <v>4000</v>
       </c>
-      <c r="D40" s="98"/>
-      <c r="E40" s="98"/>
+      <c r="D40" s="97"/>
+      <c r="E40" s="97"/>
       <c r="F40" s="77">
         <f t="shared" si="3"/>
         <v>40500</v>
       </c>
     </row>
-    <row r="41" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B41" s="100" t="s">
+    <row r="41" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="B41" s="99" t="s">
         <v>107</v>
       </c>
-      <c r="C41" s="99">
+      <c r="C41" s="98">
         <v>4000</v>
       </c>
-      <c r="D41" s="98"/>
-      <c r="E41" s="98"/>
+      <c r="D41" s="97"/>
+      <c r="E41" s="97"/>
       <c r="F41" s="77">
         <f t="shared" si="3"/>
         <v>44500</v>
       </c>
     </row>
-    <row r="42" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B42" s="100" t="s">
+    <row r="42" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="B42" s="99" t="s">
         <v>106</v>
       </c>
-      <c r="C42" s="99">
-        <v>0</v>
-      </c>
-      <c r="D42" s="98"/>
-      <c r="E42" s="98"/>
+      <c r="C42" s="98">
+        <v>0</v>
+      </c>
+      <c r="D42" s="97"/>
+      <c r="E42" s="97"/>
       <c r="F42" s="77">
         <f t="shared" si="3"/>
         <v>44500</v>
       </c>
     </row>
-    <row r="43" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B43" s="100" t="s">
+    <row r="43" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="B43" s="99" t="s">
         <v>105</v>
       </c>
-      <c r="C43" s="99">
-        <v>0</v>
-      </c>
-      <c r="D43" s="98"/>
-      <c r="E43" s="98"/>
+      <c r="C43" s="98">
+        <v>0</v>
+      </c>
+      <c r="D43" s="97"/>
+      <c r="E43" s="97"/>
       <c r="F43" s="77">
         <f t="shared" si="3"/>
         <v>44500</v>
       </c>
     </row>
-    <row r="44" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B44" s="97" t="s">
+    <row r="44" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="B44" s="96" t="s">
         <v>104</v>
       </c>
-      <c r="C44" s="96">
-        <v>0</v>
-      </c>
-      <c r="D44" s="95"/>
-      <c r="E44" s="95"/>
-      <c r="F44" s="94">
+      <c r="C44" s="95">
+        <v>0</v>
+      </c>
+      <c r="D44" s="94"/>
+      <c r="E44" s="94"/>
+      <c r="F44" s="93">
         <f t="shared" si="3"/>
         <v>44500</v>
       </c>
     </row>
-    <row r="45" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B45" s="97" t="s">
+    <row r="45" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="B45" s="96" t="s">
         <v>103</v>
       </c>
-      <c r="C45" s="96">
-        <v>0</v>
-      </c>
-      <c r="D45" s="95"/>
-      <c r="E45" s="95"/>
-      <c r="F45" s="94">
+      <c r="C45" s="95">
+        <v>0</v>
+      </c>
+      <c r="D45" s="94"/>
+      <c r="E45" s="94"/>
+      <c r="F45" s="93">
         <f>+F43+C45-D45</f>
         <v>44500</v>
       </c>
     </row>
-    <row r="46" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B46" s="97" t="s">
+    <row r="46" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="B46" s="96" t="s">
         <v>102</v>
       </c>
-      <c r="C46" s="96">
-        <v>0</v>
-      </c>
-      <c r="D46" s="95"/>
-      <c r="E46" s="95"/>
-      <c r="F46" s="94">
+      <c r="C46" s="95">
+        <v>0</v>
+      </c>
+      <c r="D46" s="94"/>
+      <c r="E46" s="94"/>
+      <c r="F46" s="93">
         <f>+F44+C46-D46</f>
         <v>44500</v>
       </c>
     </row>
-    <row r="47" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B47" s="93" t="s">
+    <row r="47" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B47" s="92" t="s">
         <v>101</v>
       </c>
-      <c r="C47" s="92">
+      <c r="C47" s="91">
         <f>-A47</f>
         <v>0</v>
       </c>
-      <c r="D47" s="91"/>
-      <c r="E47" s="91"/>
-      <c r="F47" s="90">
+      <c r="D47" s="90"/>
+      <c r="E47" s="90"/>
+      <c r="F47" s="89">
         <f>+F45+C47-D47</f>
         <v>44500</v>
       </c>
